--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2545,6 +2545,44 @@
       </c>
       <c r="F56" t="n">
         <v>77049.0546875</v>
+      </c>
+      <c r="G56" t="n">
+        <v>77201.40625</v>
+      </c>
+      <c r="H56" t="n">
+        <v>152.3515625</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.1973429888137562</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.1821566018667443</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:10</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>24</v>
+      </c>
+      <c r="F57" t="n">
+        <v>77114.15625</v>
       </c>
     </row>
   </sheetData>
@@ -2558,7 +2596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5949,6 +5987,24 @@
           <t>77226.367188,77207.531250,77218.179688,77252.718750,77218.570312,77180.078125,77184.734375,77174.148438,77187.703125,77135.015625,77111.421875,77129.546875,77103.000000,77053.328125,77108.859375,77067.312500,77076.695312,77067.125000,77079.312500,77015.312500,77074.789062,77090.390625,77046.171875,77049.054688</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>77200.000000,77279.046875,77257.000000,77340.726562,77336.023438,77311.710938,77339.796875,77319.453125,77351.601562,77438.648438,77363.968750,77337.968750,77191.421875,77126.281250,77105.429688,77152.679688,77240.789062,77219.859375,77266.421875,77252.960938,77299.531250,77268.023438,77176.070312,77201.406250</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>26.367188,71.515625,38.820312,88.007812,117.453126,131.632812,155.062500,145.304687,163.898438,303.632812,252.546875,208.421875,88.421875,72.953125,3.429688,85.367188,164.093751,152.734375,187.109375,237.648438,224.742188,177.632812,129.898438,152.351562</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0.034154,0.092542,0.050248,0.113792,0.151874,0.170262,0.200495,0.187928,0.211888,0.392095,0.326440,0.269495,0.114549,0.094589,0.004448,0.110647,0.212444,0.197792,0.242161,0.307624,0.290742,0.229892,0.168314,0.197343</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.1821566018667443</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>77113.804688,77204.875000,77164.843750,77229.085938,77276.789062,77164.835938,77177.437500,77180.757812,77056.851562,77190.398438,77088.640625,77059.632812,77016.765625,77086.640625,77101.992188,76994.421875,77010.984375,77029.140625,77062.312500,76957.429688,77096.328125,76944.570312,76988.125000,76946.921875</t>
@@ -5962,6 +6018,49 @@
       <c r="M56" t="inlineStr">
         <is>
           <t>77100.742188,76994.250000,76954.531250,76947.609375,76845.726562,76736.750000,76703.390625,76708.250000,76765.085938,76619.335938,76483.117188,76479.804688,76500.515625,76431.257812,76502.570312,76444.109375,76381.250000,76272.546875,76283.007812,76203.546875,76276.890625,76207.750000,76213.093750,76227.328125</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:10</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>24</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>77187.062500,77195.203125,77163.398438,77211.375000,77199.921875,77204.289062,77177.890625,77162.351562,77199.421875,77201.796875,77163.203125,77161.421875,77168.648438,77137.601562,77139.320312,77157.937500,77168.085938,77134.257812,77127.507812,77134.242188,77141.703125,77130.039062,77121.125000,77114.156250</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>77152.757812,77189.851562,77143.609375,77225.257812,77310.203125,77222.734375,77277.859375,77192.078125,77142.289062,77205.187500,77162.593750,77152.132812,77161.406250,77220.906250,77135.007812,77088.273438,77121.382812,77185.789062,77203.320312,77114.343750,77176.703125,77022.031250,77092.320312,77044.414062</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>77010.320312,77003.914062,76844.671875,76935.500000,76810.687500,76794.554688,76747.460938,76634.117188,76557.718750,76497.312500,76392.843750,76350.679688,76246.429688,76319.742188,76312.937500,76235.804688,76189.898438,76133.585938,75980.101562,75978.570312,76000.390625,76035.070312,75999.117188,75923.648438</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>77127.523438,77082.265625,76972.750000,77004.328125,76918.156250,76906.554688,76855.312500,76837.109375,76878.593750,76779.609375,76643.390625,76645.507812,76667.656250,76609.726562,76648.578125,76629.804688,76569.023438,76510.523438,76488.523438,76483.531250,76503.742188,76448.648438,76455.484375,76462.570312</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2583,44 @@
       </c>
       <c r="F57" t="n">
         <v>77114.15625</v>
+      </c>
+      <c r="G57" t="n">
+        <v>77543.7890625</v>
+      </c>
+      <c r="H57" t="n">
+        <v>429.6328125</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.5540518688785218</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.3430018015144455</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:30</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>24</v>
+      </c>
+      <c r="F58" t="n">
+        <v>77365.71875</v>
       </c>
     </row>
   </sheetData>
@@ -2596,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6048,6 +6086,24 @@
           <t>77187.062500,77195.203125,77163.398438,77211.375000,77199.921875,77204.289062,77177.890625,77162.351562,77199.421875,77201.796875,77163.203125,77161.421875,77168.648438,77137.601562,77139.320312,77157.937500,77168.085938,77134.257812,77127.507812,77134.242188,77141.703125,77130.039062,77121.125000,77114.156250</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>77291.429688,77099.742188,77100.179688,76778.023438,76766.093750,76623.929688,76759.132812,76730.140625,76818.078125,77177.820312,77105.273438,77256.648438,77298.593750,77312.343750,77253.718750,77313.468750,77280.578125,76676.039062,76799.851562,76767.398438,77076.828125,77569.132812,77566.500000,77543.789062</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>104.367188,95.460938,63.218751,433.351562,433.828125,580.359374,418.757812,432.210937,381.343750,23.976562,57.929688,95.226562,129.945312,174.742188,114.398438,155.531250,112.492187,458.218749,327.656249,366.843751,64.875000,439.093751,445.375000,429.632812</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0.135031,0.123815,0.081996,0.564421,0.565130,0.757413,0.545548,0.563287,0.496424,0.031067,0.075131,0.123260,0.168108,0.226021,0.148081,0.201170,0.145563,0.597604,0.426637,0.477864,0.084169,0.566068,0.574185,0.554052</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.3430018015144455</v>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>77152.757812,77189.851562,77143.609375,77225.257812,77310.203125,77222.734375,77277.859375,77192.078125,77142.289062,77205.187500,77162.593750,77152.132812,77161.406250,77220.906250,77135.007812,77088.273438,77121.382812,77185.789062,77203.320312,77114.343750,77176.703125,77022.031250,77092.320312,77044.414062</t>
@@ -6061,6 +6117,49 @@
       <c r="M57" t="inlineStr">
         <is>
           <t>77127.523438,77082.265625,76972.750000,77004.328125,76918.156250,76906.554688,76855.312500,76837.109375,76878.593750,76779.609375,76643.390625,76645.507812,76667.656250,76609.726562,76648.578125,76629.804688,76569.023438,76510.523438,76488.523438,76483.531250,76503.742188,76448.648438,76455.484375,76462.570312</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:30</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>24</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>77469.468750,77484.007812,77436.750000,77468.101562,77439.328125,77437.984375,77419.945312,77389.171875,77406.187500,77395.195312,77402.101562,77392.945312,77406.234375,77369.843750,77375.023438,77380.117188,77397.656250,77357.031250,77345.429688,77360.367188,77331.359375,77326.328125,77365.906250,77365.718750</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>77433.960938,77403.718750,77433.890625,77474.929688,77508.156250,77432.734375,77493.984375,77397.031250,77397.734375,77436.101562,77387.507812,77406.273438,77384.054688,77456.421875,77390.593750,77314.093750,77411.820312,77369.328125,77451.484375,77416.984375,77395.375000,77251.609375,77394.851562,77390.734375</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>77194.218750,77144.890625,76980.882812,77025.023438,76878.015625,76867.421875,76832.445312,76698.734375,76637.757812,76575.578125,76550.718750,76503.218750,76436.843750,76489.515625,76487.320312,76430.687500,76405.156250,76365.671875,76187.054688,76186.937500,76188.976562,76219.171875,76225.015625,76147.632812</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>77336.664062,77273.234375,77147.734375,77144.890625,77053.937500,77012.671875,77000.406250,76951.343750,76973.984375,76875.960938,76814.656250,76782.320312,76820.335938,76764.835938,76833.398438,76831.914062,76776.570312,76743.015625,76675.140625,76699.796875,76674.570312,76621.234375,76627.351562,76622.695312</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2621,6 +2621,44 @@
       </c>
       <c r="F58" t="n">
         <v>77365.71875</v>
+      </c>
+      <c r="G58" t="n">
+        <v>77517.7109375</v>
+      </c>
+      <c r="H58" t="n">
+        <v>151.9921875</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.1960741431368456</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.011828294876683</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:37:58</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>24</v>
+      </c>
+      <c r="F59" t="n">
+        <v>77569.109375</v>
       </c>
     </row>
   </sheetData>
@@ -2634,7 +2672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6147,6 +6185,24 @@
           <t>77469.468750,77484.007812,77436.750000,77468.101562,77439.328125,77437.984375,77419.945312,77389.171875,77406.187500,77395.195312,77402.101562,77392.945312,77406.234375,77369.843750,77375.023438,77380.117188,77397.656250,77357.031250,77345.429688,77360.367188,77331.359375,77326.328125,77365.906250,77365.718750</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>77574.546875,77557.562500,77855.500000,77705.031250,78101.093750,77867.453125,77736.421875,77659.242188,78159.062500,78502.710938,78552.437500,78752.828125,78941.796875,79219.789062,78973.117188,79089.382812,78742.703125,78541.289062,78192.453125,77938.062500,77893.867188,77886.789062,77636.406250,77517.710938</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>105.078125,73.554688,418.750000,236.929688,661.765625,429.468750,316.476563,270.070312,752.875000,1107.515626,1150.335938,1359.882813,1535.562500,1849.945312,1598.093749,1709.265624,1345.046875,1184.257812,847.023437,577.695312,562.507812,560.460938,270.500000,151.992188</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0.135454,0.094839,0.537855,0.304909,0.847319,0.551538,0.407115,0.347763,0.963260,1.410799,1.464418,1.726773,1.945183,2.335206,2.023592,2.161182,1.708154,1.507816,1.083255,0.741224,0.722146,0.719584,0.348419,0.196074</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>1.011828294876683</v>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>77433.960938,77403.718750,77433.890625,77474.929688,77508.156250,77432.734375,77493.984375,77397.031250,77397.734375,77436.101562,77387.507812,77406.273438,77384.054688,77456.421875,77390.593750,77314.093750,77411.820312,77369.328125,77451.484375,77416.984375,77395.375000,77251.609375,77394.851562,77390.734375</t>
@@ -6160,6 +6216,49 @@
       <c r="M58" t="inlineStr">
         <is>
           <t>77336.664062,77273.234375,77147.734375,77144.890625,77053.937500,77012.671875,77000.406250,76951.343750,76973.984375,76875.960938,76814.656250,76782.320312,76820.335938,76764.835938,76833.398438,76831.914062,76776.570312,76743.015625,76675.140625,76699.796875,76674.570312,76621.234375,76627.351562,76622.695312</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:37:58</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>24</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>77466.585938,77463.414062,77458.593750,77530.718750,77498.351562,77524.703125,77536.937500,77557.445312,77586.484375,77602.132812,77609.507812,77631.015625,77619.632812,77596.750000,77628.523438,77620.453125,77633.757812,77616.507812,77611.835938,77623.539062,77586.031250,77567.382812,77582.000000,77569.109375</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>77430.492188,77338.125000,77460.406250,77552.460938,77536.570312,77517.726562,77618.765625,77555.875000,77523.085938,77686.031250,77600.960938,77553.640625,77579.992188,77718.468750,77581.898438,77563.820312,77675.046875,77629.304688,77615.250000,77651.468750,77579.445312,77424.335938,77594.375000,77578.015625</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>77212.921875,77175.921875,77051.625000,77097.890625,76953.531250,76915.390625,76865.117188,76785.601562,76768.484375,76712.515625,76648.757812,76618.351562,76551.679688,76653.812500,76629.507812,76617.031250,76601.406250,76548.976562,76391.859375,76374.632812,76413.390625,76424.781250,76472.554688,76378.273438</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>77331.125000,77277.609375,77194.421875,77229.546875,77107.203125,77067.601562,77074.765625,77064.789062,77136.039062,77027.742188,76971.976562,76928.492188,76978.578125,76980.062500,76988.812500,77019.117188,77019.148438,76936.882812,76935.718750,76961.781250,76937.609375,76869.578125,76844.843750,76856.867188</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2659,6 +2659,44 @@
       </c>
       <c r="F59" t="n">
         <v>77569.109375</v>
+      </c>
+      <c r="G59" t="n">
+        <v>75808.703125</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1760.40625</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2.322169061640968</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.661180377218328</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:13</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>24</v>
+      </c>
+      <c r="F60" t="n">
+        <v>76040.46875</v>
       </c>
     </row>
   </sheetData>
@@ -2672,7 +2710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6246,6 +6284,24 @@
           <t>77466.585938,77463.414062,77458.593750,77530.718750,77498.351562,77524.703125,77536.937500,77557.445312,77586.484375,77602.132812,77609.507812,77631.015625,77619.632812,77596.750000,77628.523438,77620.453125,77633.757812,77616.507812,77611.835938,77623.539062,77586.031250,77567.382812,77582.000000,77569.109375</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>77609.070312,77261.828125,76879.476562,76955.062500,76946.718750,77014.593750,76895.187500,76924.929688,76568.062500,75853.890625,76467.992188,76338.851562,76907.851562,75945.390625,76124.687500,75871.398438,75414.726562,75611.000000,75584.179688,75712.210938,75434.593750,75824.851562,75755.421875,75808.703125</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>142.484374,201.585937,579.117188,575.656250,551.632812,510.109375,641.750000,632.515624,1018.421875,1748.242187,1141.515624,1292.164062,711.781249,1651.359375,1503.835938,1749.054688,2219.031249,2005.507812,2027.656251,1911.328124,2151.437500,1742.531249,1826.578125,1760.406250</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0.183592,0.260913,0.753279,0.748042,0.716902,0.662354,0.834578,0.822251,1.330087,2.304750,1.492802,1.692669,0.925499,2.174404,1.975490,2.305289,2.942438,2.652402,2.682646,2.524465,2.852057,2.298100,2.411152,2.322169</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>1.661180377218328</v>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>77430.492188,77338.125000,77460.406250,77552.460938,77536.570312,77517.726562,77618.765625,77555.875000,77523.085938,77686.031250,77600.960938,77553.640625,77579.992188,77718.468750,77581.898438,77563.820312,77675.046875,77629.304688,77615.250000,77651.468750,77579.445312,77424.335938,77594.375000,77578.015625</t>
@@ -6259,6 +6315,49 @@
       <c r="M59" t="inlineStr">
         <is>
           <t>77331.125000,77277.609375,77194.421875,77229.546875,77107.203125,77067.601562,77074.765625,77064.789062,77136.039062,77027.742188,76971.976562,76928.492188,76978.578125,76980.062500,76988.812500,77019.117188,77019.148438,76936.882812,76935.718750,76961.781250,76937.609375,76869.578125,76844.843750,76856.867188</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:13</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>24</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>75779.460938,75782.539062,75779.898438,75797.093750,75815.062500,75856.703125,75869.203125,75853.421875,75897.234375,75960.992188,75887.890625,75940.687500,75960.085938,75946.125000,75996.023438,76022.421875,75996.914062,75997.937500,76008.125000,76016.671875,76039.703125,76052.914062,76014.554688,76040.468750</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>75818.929688,75807.734375,75700.789062,75833.601562,75932.000000,75947.632812,76037.507812,75826.101562,75970.531250,76042.960938,75971.875000,76083.710938,76146.539062,76208.820312,76138.187500,75912.539062,76175.351562,76253.687500,76208.125000,76109.953125,76177.742188,75876.484375,76123.226562,76147.304688</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>75363.062500,75344.414062,75161.195312,75154.046875,75039.812500,75013.593750,75071.656250,74956.734375,74894.054688,74904.101562,74716.476562,74749.242188,74671.304688,74704.898438,74738.640625,74680.289062,74600.156250,74527.218750,74330.437500,74301.687500,74344.023438,74401.398438,74346.835938,74348.148438</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>75576.054688,75500.468750,75387.710938,75351.757812,75295.562500,75280.710938,75325.265625,75255.812500,75349.093750,75323.609375,75118.687500,75186.648438,75178.109375,75140.937500,75224.929688,75197.312500,75099.171875,75007.234375,75011.320312,75006.890625,75032.523438,74986.070312,74973.734375,75032.359375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2697,6 +2697,44 @@
       </c>
       <c r="F60" t="n">
         <v>76040.46875</v>
+      </c>
+      <c r="G60" t="n">
+        <v>76206.046875</v>
+      </c>
+      <c r="H60" t="n">
+        <v>165.578125</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.2172768852209276</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.2591007412563935</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:37</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>24</v>
+      </c>
+      <c r="F61" t="n">
+        <v>76262.171875</v>
       </c>
     </row>
   </sheetData>
@@ -2710,7 +2748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6345,6 +6383,24 @@
           <t>75779.460938,75782.539062,75779.898438,75797.093750,75815.062500,75856.703125,75869.203125,75853.421875,75897.234375,75960.992188,75887.890625,75940.687500,75960.085938,75946.125000,75996.023438,76022.421875,75996.914062,75997.937500,76008.125000,76016.671875,76039.703125,76052.914062,76014.554688,76040.468750</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>75900.460938,75969.000000,75693.531250,75670.390625,75924.046875,75885.507812,76182.140625,75902.296875,75582.093750,75618.976562,75729.312500,75701.609375,75734.093750,75538.703125,76010.210938,76102.968750,75907.460938,75620.078125,76179.718750,76273.320312,76295.312500,76303.742188,76364.562500,76206.046875</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>120.999999,186.460938,86.367188,126.703125,108.984375,28.804688,312.937500,48.875000,315.140625,342.015626,158.578125,239.078125,225.992188,407.421875,14.187499,80.546875,89.453124,377.859375,171.593750,256.648438,255.609375,250.828126,350.007812,165.578125</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0.159419,0.245443,0.114101,0.167441,0.143544,0.037958,0.410775,0.064392,0.416951,0.452288,0.209401,0.315816,0.298402,0.539355,0.018665,0.105839,0.117845,0.499681,0.225249,0.336485,0.335026,0.328723,0.458338,0.217277</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.2591007412563935</v>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>75818.929688,75807.734375,75700.789062,75833.601562,75932.000000,75947.632812,76037.507812,75826.101562,75970.531250,76042.960938,75971.875000,76083.710938,76146.539062,76208.820312,76138.187500,75912.539062,76175.351562,76253.687500,76208.125000,76109.953125,76177.742188,75876.484375,76123.226562,76147.304688</t>
@@ -6358,6 +6414,49 @@
       <c r="M60" t="inlineStr">
         <is>
           <t>75576.054688,75500.468750,75387.710938,75351.757812,75295.562500,75280.710938,75325.265625,75255.812500,75349.093750,75323.609375,75118.687500,75186.648438,75178.109375,75140.937500,75224.929688,75197.312500,75099.171875,75007.234375,75011.320312,75006.890625,75032.523438,74986.070312,74973.734375,75032.359375</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:37</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>24</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>76181.296875,76208.398438,76209.257812,76229.226562,76235.820312,76251.046875,76274.148438,76274.320312,76292.851562,76274.914062,76284.695312,76313.578125,76276.312500,76271.609375,76309.085938,76306.734375,76268.273438,76301.117188,76282.671875,76266.671875,76289.054688,76298.492188,76276.750000,76262.171875</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>76152.859375,76167.906250,76130.414062,76233.445312,76269.187500,76233.054688,76371.664062,76256.914062,76198.062500,76365.468750,76235.765625,76347.007812,76397.117188,76408.078125,76407.343750,76262.546875,76423.429688,76385.875000,76382.367188,76333.265625,76395.609375,76163.351562,76296.796875,76310.734375</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>75974.078125,75932.304688,75798.648438,75815.242188,75727.281250,75673.445312,75686.750000,75614.921875,75550.328125,75482.281250,75414.203125,75375.078125,75261.382812,75291.445312,75343.781250,75250.820312,75167.695312,75130.054688,74906.546875,74815.804688,74911.539062,74927.539062,74920.492188,74826.718750</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>76100.617188,76052.304688,75967.625000,75956.500000,75916.492188,75867.117188,75885.359375,75886.257812,75915.820312,75810.531250,75717.375000,75726.335938,75670.093750,75632.820312,75702.265625,75702.093750,75585.585938,75541.414062,75508.164062,75460.835938,75472.671875,75449.617188,75463.375000,75453.875000</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2735,6 +2735,44 @@
       </c>
       <c r="F61" t="n">
         <v>76262.171875</v>
+      </c>
+      <c r="G61" t="n">
+        <v>77224.2578125</v>
+      </c>
+      <c r="H61" t="n">
+        <v>962.0859375</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.245833841272957</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.3859815295090727</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:23:53</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>24</v>
+      </c>
+      <c r="F62" t="n">
+        <v>77063.9140625</v>
       </c>
     </row>
   </sheetData>
@@ -2748,7 +2786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6444,6 +6482,24 @@
           <t>76181.296875,76208.398438,76209.257812,76229.226562,76235.820312,76251.046875,76274.148438,76274.320312,76292.851562,76274.914062,76284.695312,76313.578125,76276.312500,76271.609375,76309.085938,76306.734375,76268.273438,76301.117188,76282.671875,76266.671875,76289.054688,76298.492188,76276.750000,76262.171875</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>76250.976562,76402.921875,76377.570312,76497.640625,76395.937500,76329.953125,76400.992188,76659.828125,76612.257812,76423.617188,76676.421875,76688.007812,76606.828125,76506.398438,76543.343750,76498.539062,76352.546875,76359.867188,76348.742188,76526.101562,76659.398438,76910.796875,77297.703125,77224.257812</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>69.679688,194.523437,168.312501,268.414063,160.117188,78.906250,126.843749,385.507813,319.406251,148.703126,391.726563,374.429688,330.515625,234.789062,234.257812,191.804688,84.273437,58.749999,66.070312,259.429688,370.343749,612.304687,1020.953125,962.085938</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.091382,0.254602,0.220369,0.350879,0.209589,0.103375,0.166024,0.502881,0.416913,0.194577,0.510883,0.488251,0.431444,0.306888,0.306046,0.250730,0.110374,0.076938,0.086538,0.339008,0.483103,0.796123,1.320807,1.245834</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0.3859815295090727</v>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>76152.859375,76167.906250,76130.414062,76233.445312,76269.187500,76233.054688,76371.664062,76256.914062,76198.062500,76365.468750,76235.765625,76347.007812,76397.117188,76408.078125,76407.343750,76262.546875,76423.429688,76385.875000,76382.367188,76333.265625,76395.609375,76163.351562,76296.796875,76310.734375</t>
@@ -6457,6 +6513,49 @@
       <c r="M61" t="inlineStr">
         <is>
           <t>76100.617188,76052.304688,75967.625000,75956.500000,75916.492188,75867.117188,75885.359375,75886.257812,75915.820312,75810.531250,75717.375000,75726.335938,75670.093750,75632.820312,75702.265625,75702.093750,75585.585938,75541.414062,75508.164062,75460.835938,75472.671875,75449.617188,75463.375000,75453.875000</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:23:53</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>24</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>77186.273438,77197.453125,77196.164062,77249.828125,77221.796875,77214.976562,77199.281250,77178.492188,77209.093750,77179.007812,77169.460938,77181.234375,77140.218750,77102.515625,77127.109375,77130.476562,77121.882812,77090.296875,77080.171875,77077.421875,77103.515625,77070.742188,77058.679688,77063.914062</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>77155.406250,77160.929688,77089.398438,77275.578125,77253.578125,77177.554688,77239.312500,77150.765625,77122.093750,77238.625000,77159.421875,77134.562500,77172.328125,77209.109375,77139.640625,77096.296875,77193.226562,77147.664062,77118.273438,77084.218750,77032.906250,77065.109375,77032.789062,77051.414062</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>76839.765625,76782.445312,76657.976562,76699.125000,76556.117188,76498.804688,76465.093750,76391.578125,76334.398438,76244.960938,76198.804688,76159.773438,76013.234375,76059.109375,76052.789062,75992.562500,75923.593750,75848.453125,75659.195312,75598.671875,75650.437500,75660.914062,75626.914062,75542.632812</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>77030.757812,76946.703125,76872.054688,76871.351562,76791.382812,76708.195312,76697.468750,76673.734375,76716.046875,76595.250000,76488.250000,76465.328125,76439.726562,76388.937500,76429.140625,76436.585938,76355.976562,76296.328125,76217.359375,76230.734375,76230.843750,76152.500000,76162.773438,76181.203125</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2773,6 +2773,44 @@
       </c>
       <c r="F62" t="n">
         <v>77063.9140625</v>
+      </c>
+      <c r="G62" t="n">
+        <v>81109.9296875</v>
+      </c>
+      <c r="H62" t="n">
+        <v>4046.015625</v>
+      </c>
+      <c r="I62" t="n">
+        <v>4.988311099009051</v>
+      </c>
+      <c r="J62" t="n">
+        <v>3.504184089477507</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:46</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>24</v>
+      </c>
+      <c r="F63" t="n">
+        <v>80201.703125</v>
       </c>
     </row>
   </sheetData>
@@ -2786,7 +2824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6543,6 +6581,24 @@
           <t>77186.273438,77197.453125,77196.164062,77249.828125,77221.796875,77214.976562,77199.281250,77178.492188,77209.093750,77179.007812,77169.460938,77181.234375,77140.218750,77102.515625,77127.109375,77130.476562,77121.882812,77090.296875,77080.171875,77077.421875,77103.515625,77070.742188,77058.679688,77063.914062</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>77426.773438,77527.382812,77734.781250,78200.000000,78148.140625,78221.460938,77995.187500,77979.593750,80026.992188,80904.093750,80698.242188,80829.000000,80992.593750,80916.382812,81180.000000,81096.187500,81223.781250,81124.523438,80875.101562,81654.632812,81262.507812,81261.007812,81105.031250,81109.929688</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>240.499999,329.929688,538.617188,950.171875,926.343750,1006.484376,795.906250,801.101562,2817.898438,3725.085938,3528.781249,3647.765625,3852.375000,3813.867188,4052.890625,3965.710938,4101.898438,4034.226562,3794.929688,4577.210938,4158.992188,4190.265624,4046.351562,4046.015626</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0.310616,0.425565,0.692891,1.215054,1.185369,1.286711,1.020456,1.027322,3.521185,4.604323,4.372811,4.512942,4.756453,4.713344,4.992474,4.890132,5.050120,4.972882,4.692334,5.605574,5.117972,5.156551,4.989027,4.988311</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>3.504184089477507</v>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>77155.406250,77160.929688,77089.398438,77275.578125,77253.578125,77177.554688,77239.312500,77150.765625,77122.093750,77238.625000,77159.421875,77134.562500,77172.328125,77209.109375,77139.640625,77096.296875,77193.226562,77147.664062,77118.273438,77084.218750,77032.906250,77065.109375,77032.789062,77051.414062</t>
@@ -6556,6 +6612,49 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>77030.757812,76946.703125,76872.054688,76871.351562,76791.382812,76708.195312,76697.468750,76673.734375,76716.046875,76595.250000,76488.250000,76465.328125,76439.726562,76388.937500,76429.140625,76436.585938,76355.976562,76296.328125,76217.359375,76230.734375,76230.843750,76152.500000,76162.773438,76181.203125</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:46</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>24</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>81067.085938,81047.421875,81066.687500,81004.875000,80937.820312,80962.226562,80900.312500,80798.687500,80851.273438,80786.648438,80784.015625,80724.179688,80664.812500,80578.328125,80597.914062,80469.554688,80500.875000,80443.257812,80387.187500,80340.523438,80301.796875,80280.671875,80253.812500,80201.703125</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>81007.734375,80866.929688,80942.195312,80996.703125,80793.109375,80865.648438,80637.859375,80689.335938,80628.476562,80765.210938,80625.546875,80474.265625,80337.125000,80490.750000,80375.851562,80328.679688,80269.554688,80044.226562,80129.828125,80186.445312,80018.968750,80144.484375,80039.687500,79895.437500</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>80527.023438,80421.039062,80262.554688,80119.820312,79852.703125,79724.000000,79484.156250,79316.460938,79240.593750,79087.960938,78932.125000,78805.054688,78697.179688,78699.171875,78523.578125,78441.953125,78348.421875,78284.617188,77935.453125,77878.031250,77787.593750,77849.882812,77735.726562,77722.750000</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>80855.476562,80706.554688,80643.226562,80557.140625,80313.484375,80204.070312,80046.093750,79916.140625,80006.671875,79840.773438,79730.664062,79566.945312,79562.679688,79456.187500,79393.250000,79292.226562,79314.953125,79171.968750,79024.054688,78990.929688,78912.898438,78749.851562,78733.257812,78767.921875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2811,6 +2811,44 @@
       </c>
       <c r="F63" t="n">
         <v>80201.703125</v>
+      </c>
+      <c r="G63" t="n">
+        <v>80442.421875</v>
+      </c>
+      <c r="H63" t="n">
+        <v>240.71875</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.2992435389054477</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.6380058169309644</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:39:50</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>24</v>
+      </c>
+      <c r="F64" t="n">
+        <v>79888.4453125</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +2862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6642,6 +6680,24 @@
           <t>81067.085938,81047.421875,81066.687500,81004.875000,80937.820312,80962.226562,80900.312500,80798.687500,80851.273438,80786.648438,80784.015625,80724.179688,80664.812500,80578.328125,80597.914062,80469.554688,80500.875000,80443.257812,80387.187500,80340.523438,80301.796875,80280.671875,80253.812500,80201.703125</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>81022.500000,81013.562500,81061.148438,81297.648438,81298.843750,81189.601562,81280.000000,81309.992188,81325.000000,81554.890625,81610.820312,81813.351562,81437.101562,81412.242188,81344.023438,81129.976562,81063.726562,81232.468750,81276.359375,81277.492188,81071.710938,80312.476562,80458.390625,80442.421875</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>44.585938,33.859375,5.539062,292.773438,361.023438,227.375001,379.687500,511.304688,473.726562,768.242187,826.804688,1089.171874,772.289062,833.914062,746.109376,660.421874,562.851562,789.210938,889.171875,936.968749,769.914062,31.804688,204.578125,240.718750</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0.055029,0.041795,0.006833,0.360125,0.444070,0.280054,0.467135,0.628834,0.582510,0.941994,1.013107,1.331289,0.948326,1.024310,0.917227,0.814029,0.694332,0.971546,1.094010,1.152802,0.949670,0.039601,0.254266,0.299244</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0.6380058169309644</v>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>81007.734375,80866.929688,80942.195312,80996.703125,80793.109375,80865.648438,80637.859375,80689.335938,80628.476562,80765.210938,80625.546875,80474.265625,80337.125000,80490.750000,80375.851562,80328.679688,80269.554688,80044.226562,80129.828125,80186.445312,80018.968750,80144.484375,80039.687500,79895.437500</t>
@@ -6655,6 +6711,49 @@
       <c r="M63" t="inlineStr">
         <is>
           <t>80855.476562,80706.554688,80643.226562,80557.140625,80313.484375,80204.070312,80046.093750,79916.140625,80006.671875,79840.773438,79730.664062,79566.945312,79562.679688,79456.187500,79393.250000,79292.226562,79314.953125,79171.968750,79024.054688,78990.929688,78912.898438,78749.851562,78733.257812,78767.921875</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:39:50</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>24</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>80447.531250,80407.000000,80393.507812,80355.375000,80331.359375,80339.171875,80301.375000,80231.117188,80254.132812,80221.460938,80211.953125,80185.710938,80176.929688,80139.937500,80147.523438,80105.015625,80127.546875,80093.835938,80036.656250,80040.812500,80001.156250,79961.382812,79952.554688,79888.445312</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>80394.187500,80308.476562,80303.398438,80342.664062,80352.500000,80250.382812,80174.265625,80194.257812,80174.515625,80123.875000,80203.906250,80121.664062,80004.546875,80146.867188,79998.578125,79998.078125,80011.609375,79827.359375,79930.609375,79921.820312,79811.070312,79867.218750,79856.875000,79758.921875</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>80072.359375,80015.843750,79839.640625,79723.671875,79563.609375,79456.992188,79334.132812,79193.843750,79065.898438,78949.054688,78772.085938,78753.570312,78639.617188,78614.554688,78495.437500,78469.843750,78398.742188,78396.585938,78043.421875,77998.750000,77924.453125,77946.781250,77850.968750,77773.679688</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>80299.445312,80159.578125,80073.796875,79995.304688,79886.429688,79812.007812,79703.328125,79600.515625,79626.281250,79520.289062,79372.250000,79347.062500,79303.085938,79202.632812,79167.414062,79186.250000,79106.554688,79110.914062,78943.414062,78955.015625,78864.000000,78739.671875,78698.859375,78660.273438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2849,6 +2849,44 @@
       </c>
       <c r="F64" t="n">
         <v>79888.4453125</v>
+      </c>
+      <c r="G64" t="n">
+        <v>81346.4765625</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1458.03125</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1.792371730912977</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.8729392585229817</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:45</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>24</v>
+      </c>
+      <c r="F65" t="n">
+        <v>80946.1640625</v>
       </c>
     </row>
   </sheetData>
@@ -2862,7 +2900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6741,6 +6779,24 @@
           <t>80447.531250,80407.000000,80393.507812,80355.375000,80331.359375,80339.171875,80301.375000,80231.117188,80254.132812,80221.460938,80211.953125,80185.710938,80176.929688,80139.937500,80147.523438,80105.015625,80127.546875,80093.835938,80036.656250,80040.812500,80001.156250,79961.382812,79952.554688,79888.445312</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>80456.007812,80272.500000,80284.562500,80228.203125,80430.007812,80283.007812,80442.976562,80451.140625,80522.046875,80639.539062,80874.203125,81311.992188,81129.328125,81021.218750,81162.437500,81073.468750,80916.046875,81196.492188,81159.539062,81604.820312,80981.781250,81299.859375,81411.500000,81346.476562</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>8.476562,134.500000,108.945312,127.171875,98.648438,56.164062,141.601562,220.023437,267.914063,418.078124,662.250000,1126.281249,952.398437,881.281250,1014.914062,968.453125,788.500000,1102.656249,1122.882812,1564.007812,980.625000,1338.476563,1458.945312,1458.031251</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0.010536,0.167554,0.135699,0.158513,0.122651,0.069958,0.176027,0.273487,0.332721,0.518453,0.818864,1.385135,1.173926,1.087717,1.250473,1.194538,0.974467,1.358010,1.383550,1.916563,1.210921,1.646345,1.792063,1.792372</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>0.8729392585229817</v>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>80394.187500,80308.476562,80303.398438,80342.664062,80352.500000,80250.382812,80174.265625,80194.257812,80174.515625,80123.875000,80203.906250,80121.664062,80004.546875,80146.867188,79998.578125,79998.078125,80011.609375,79827.359375,79930.609375,79921.820312,79811.070312,79867.218750,79856.875000,79758.921875</t>
@@ -6754,6 +6810,49 @@
       <c r="M64" t="inlineStr">
         <is>
           <t>80299.445312,80159.578125,80073.796875,79995.304688,79886.429688,79812.007812,79703.328125,79600.515625,79626.281250,79520.289062,79372.250000,79347.062500,79303.085938,79202.632812,79167.414062,79186.250000,79106.554688,79110.914062,78943.414062,78955.015625,78864.000000,78739.671875,78698.859375,78660.273438</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:45</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>24</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>81346.976562,81326.085938,81294.742188,81306.828125,81312.289062,81322.171875,81253.164062,81210.429688,81249.835938,81207.437500,81178.203125,81173.070312,81172.867188,81124.140625,81094.398438,81105.585938,81116.296875,81060.343750,81041.804688,81023.031250,81068.359375,80981.835938,80987.335938,80946.164062</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>81249.382812,81234.257812,81290.007812,81350.570312,81356.039062,81238.710938,81108.867188,81287.375000,81187.515625,81169.796875,81153.445312,81193.898438,81063.296875,81116.625000,80965.960938,81064.335938,80991.664062,80925.781250,80985.710938,80940.945312,80864.023438,80945.156250,80898.945312,80812.054688</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>80937.382812,80916.906250,80769.851562,80788.500000,80685.000000,80602.664062,80532.625000,80433.210938,80313.609375,80201.171875,80084.000000,80094.179688,80016.984375,79982.296875,79863.015625,79906.304688,79853.203125,79850.359375,79524.734375,79418.617188,79473.203125,79425.742188,79336.093750,79222.500000</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>81136.781250,81062.742188,80997.835938,80972.312500,80946.695312,80881.570312,80811.109375,80750.679688,80754.851562,80657.468750,80522.140625,80550.101562,80601.101562,80451.570312,80394.453125,80470.179688,80397.476562,80409.125000,80249.234375,80225.531250,80200.250000,80067.578125,79996.601562,79972.054688</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,6 +2887,44 @@
       </c>
       <c r="F65" t="n">
         <v>80946.1640625</v>
+      </c>
+      <c r="G65" t="n">
+        <v>85476.8984375</v>
+      </c>
+      <c r="H65" t="n">
+        <v>4530.734375</v>
+      </c>
+      <c r="I65" t="n">
+        <v>5.300536703859038</v>
+      </c>
+      <c r="J65" t="n">
+        <v>4.686660009420585</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:42</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" t="n">
+        <v>84729.7265625</v>
       </c>
     </row>
   </sheetData>
@@ -2900,7 +2938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6840,6 +6878,24 @@
           <t>81346.976562,81326.085938,81294.742188,81306.828125,81312.289062,81322.171875,81253.164062,81210.429688,81249.835938,81207.437500,81178.203125,81173.070312,81172.867188,81124.140625,81094.398438,81105.585938,81116.296875,81060.343750,81041.804688,81023.031250,81068.359375,80981.835938,80987.335938,80946.164062</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>81541.937500,81621.539062,81706.867188,83751.796875,84637.289062,84416.578125,84863.609375,85317.320312,85432.117188,85834.523438,85933.156250,85968.953125,85902.117188,86071.781250,86501.828125,86989.898438,86557.296875,86423.117188,86591.750000,85879.500000,85598.656250,85700.000000,85675.000000,85476.898438</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>194.960938,295.453124,412.124999,2444.968750,3325.000001,3094.406250,3610.445313,4106.890624,4182.281249,4627.085938,4754.953125,4795.882813,4729.249999,4947.640625,5407.429687,5884.312499,5441.000000,5362.773438,5549.945312,4856.468750,4530.296875,4718.164062,4687.664062,4530.734376</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0.239093,0.361979,0.504395,2.919303,3.928528,3.665638,4.254409,4.813666,4.895444,5.390705,5.533316,5.578622,5.505394,5.748273,6.251232,6.764363,6.286010,6.205253,6.409323,5.654980,5.292486,5.505442,5.471449,5.300537</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>4.686660009420585</v>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>81249.382812,81234.257812,81290.007812,81350.570312,81356.039062,81238.710938,81108.867188,81287.375000,81187.515625,81169.796875,81153.445312,81193.898438,81063.296875,81116.625000,80965.960938,81064.335938,80991.664062,80925.781250,80985.710938,80940.945312,80864.023438,80945.156250,80898.945312,80812.054688</t>
@@ -6853,6 +6909,49 @@
       <c r="M65" t="inlineStr">
         <is>
           <t>81136.781250,81062.742188,80997.835938,80972.312500,80946.695312,80881.570312,80811.109375,80750.679688,80754.851562,80657.468750,80522.140625,80550.101562,80601.101562,80451.570312,80394.453125,80470.179688,80397.476562,80409.125000,80249.234375,80225.531250,80200.250000,80067.578125,79996.601562,79972.054688</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:42</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>85394.218750,85302.164062,85278.218750,85318.000000,85228.750000,85284.703125,85263.453125,85207.140625,85289.367188,85170.710938,85191.304688,85142.953125,85030.164062,84998.250000,84979.539062,84936.171875,85000.062500,84918.257812,84962.578125,84835.484375,84922.046875,84802.945312,84767.773438,84729.726562</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>85187.406250,85156.023438,85227.328125,85371.171875,85094.382812,85231.046875,84941.664062,85222.703125,85014.718750,85186.468750,85099.625000,85060.710938,84760.757812,84881.062500,84731.500000,84849.523438,84859.835938,84683.062500,84749.750000,84784.390625,84777.812500,84734.859375,84535.726562,84422.625000</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>84732.195312,84594.015625,84408.148438,84362.000000,84221.000000,84121.312500,84034.117188,83890.882812,83862.078125,83626.890625,83572.226562,83493.414062,83458.679688,83317.890625,83063.296875,83039.859375,83041.640625,82968.085938,82639.601562,82306.031250,82407.320312,82289.265625,82156.820312,82129.898438</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>85024.328125,84860.382812,84752.578125,84775.578125,84634.906250,84576.210938,84554.015625,84368.335938,84483.437500,84286.312500,84249.273438,84164.828125,84109.242188,83987.632812,83809.937500,83855.750000,83817.101562,83685.101562,83577.734375,83436.468750,83451.679688,83128.593750,83096.765625,83101.265625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2925,6 +2925,44 @@
       </c>
       <c r="F66" t="n">
         <v>84729.7265625</v>
+      </c>
+      <c r="G66" t="n">
+        <v>87018.2421875</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2288.515625</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2.629926286110087</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1.303082524035154</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:07</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>24</v>
+      </c>
+      <c r="F67" t="n">
+        <v>87017.9140625</v>
       </c>
     </row>
   </sheetData>
@@ -2938,7 +2976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6939,6 +6977,24 @@
           <t>85394.218750,85302.164062,85278.218750,85318.000000,85228.750000,85284.703125,85263.453125,85207.140625,85289.367188,85170.710938,85191.304688,85142.953125,85030.164062,84998.250000,84979.539062,84936.171875,85000.062500,84918.257812,84962.578125,84835.484375,84922.046875,84802.945312,84767.773438,84729.726562</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>85392.796875,85359.226562,85333.500000,86198.789062,86238.820312,85875.023438,85969.070312,86008.429688,86328.789062,86255.257812,86418.453125,86451.609375,86587.578125,86469.578125,86236.921875,86262.570312,86187.023438,86121.859375,86198.046875,86451.929688,86366.468750,86544.210938,86696.406250,87018.242188</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>1.421875,57.062501,55.281250,880.789062,1010.070312,590.320312,705.617188,801.289062,1039.421874,1084.546874,1227.148437,1308.656250,1557.414063,1471.328125,1257.382813,1326.398438,1186.960938,1203.601563,1235.468750,1616.445312,1444.421875,1741.265626,1928.632812,2288.515626</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0.001665,0.066850,0.064783,1.021811,1.171248,0.687418,0.820780,0.931640,1.204027,1.257369,1.420007,1.513744,1.798658,1.701556,1.458056,1.537629,1.377192,1.397556,1.433291,1.869762,1.672434,2.011995,2.224582,2.629926</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>1.303082524035154</v>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>85187.406250,85156.023438,85227.328125,85371.171875,85094.382812,85231.046875,84941.664062,85222.703125,85014.718750,85186.468750,85099.625000,85060.710938,84760.757812,84881.062500,84731.500000,84849.523438,84859.835938,84683.062500,84749.750000,84784.390625,84777.812500,84734.859375,84535.726562,84422.625000</t>
@@ -6952,6 +7008,49 @@
       <c r="M66" t="inlineStr">
         <is>
           <t>85024.328125,84860.382812,84752.578125,84775.578125,84634.906250,84576.210938,84554.015625,84368.335938,84483.437500,84286.312500,84249.273438,84164.828125,84109.242188,83987.632812,83809.937500,83855.750000,83817.101562,83685.101562,83577.734375,83436.468750,83451.679688,83128.593750,83096.765625,83101.265625</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:07</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>24</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>87013.367188,87032.750000,87039.320312,87130.679688,87039.382812,87138.726562,87102.812500,87071.445312,87154.093750,87061.953125,87067.953125,87062.500000,87011.992188,87006.187500,86997.781250,87013.718750,87137.156250,87034.859375,87080.460938,87016.546875,87114.265625,87049.218750,87079.460938,87017.914062</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>86791.273438,86865.585938,87016.773438,87156.984375,86946.375000,86999.132812,86843.000000,87132.257812,86793.742188,86978.382812,86949.531250,86952.273438,86807.453125,86900.617188,86742.546875,86845.250000,86868.250000,86769.023438,86871.679688,86895.921875,86905.000000,86959.242188,86786.562500,86745.398438</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>86345.531250,86335.359375,86206.093750,86253.296875,86213.343750,86189.968750,86108.742188,86023.234375,86033.687500,85821.398438,85787.390625,85695.671875,85671.453125,85505.304688,85372.648438,85358.562500,85427.656250,85377.171875,85133.671875,84828.929688,84923.296875,84816.695312,84761.804688,84681.843750</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>86637.781250,86607.867188,86598.171875,86668.953125,86570.046875,86569.546875,86596.671875,86473.359375,86537.625000,86392.437500,86358.203125,86322.273438,86333.945312,86122.539062,86041.265625,86132.781250,86146.171875,86067.242188,85962.531250,85823.046875,85856.710938,85666.648438,85669.906250,85646.382812</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2963,6 +2963,44 @@
       </c>
       <c r="F67" t="n">
         <v>87017.9140625</v>
+      </c>
+      <c r="G67" t="n">
+        <v>83867.21875</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3150.6953125</v>
+      </c>
+      <c r="I67" t="n">
+        <v>3.756766182853775</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2.565746226601133</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:19</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>24</v>
+      </c>
+      <c r="F68" t="n">
+        <v>83390.515625</v>
       </c>
     </row>
   </sheetData>
@@ -2976,7 +3014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7038,6 +7076,24 @@
           <t>87013.367188,87032.750000,87039.320312,87130.679688,87039.382812,87138.726562,87102.812500,87071.445312,87154.093750,87061.953125,87067.953125,87062.500000,87011.992188,87006.187500,86997.781250,87013.718750,87137.156250,87034.859375,87080.460938,87016.546875,87114.265625,87049.218750,87079.460938,87017.914062</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>86485.632812,86456.523438,86128.156250,85901.812500,85848.859375,85906.656250,85632.039062,85482.101562,85780.117188,84521.351562,84001.882812,84027.109375,84312.828125,84313.007812,84509.820312,84235.351562,84400.000000,84551.289062,84369.007812,84309.453125,84095.109375,84349.882812,83928.156250,83867.218750</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>527.734376,576.226562,911.164062,1228.867188,1190.523437,1232.070312,1470.773438,1589.343749,1373.976562,2540.601562,3066.070312,3035.390625,2699.164063,2693.179688,2487.960938,2778.367188,2737.156250,2483.570312,2711.453126,2707.093750,3019.156250,2699.335938,3151.304688,3150.695312</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>0.610199,0.666493,1.057917,1.430549,1.386767,1.434197,1.717550,1.859271,1.601742,3.005870,3.650002,3.612394,3.201368,3.194264,2.943990,3.298339,3.243076,2.937354,3.213802,3.210902,3.590169,3.200166,3.754765,3.756766</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>2.565746226601133</v>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>86791.273438,86865.585938,87016.773438,87156.984375,86946.375000,86999.132812,86843.000000,87132.257812,86793.742188,86978.382812,86949.531250,86952.273438,86807.453125,86900.617188,86742.546875,86845.250000,86868.250000,86769.023438,86871.679688,86895.921875,86905.000000,86959.242188,86786.562500,86745.398438</t>
@@ -7051,6 +7107,49 @@
       <c r="M67" t="inlineStr">
         <is>
           <t>86637.781250,86607.867188,86598.171875,86668.953125,86570.046875,86569.546875,86596.671875,86473.359375,86537.625000,86392.437500,86358.203125,86322.273438,86333.945312,86122.539062,86041.265625,86132.781250,86146.171875,86067.242188,85962.531250,85823.046875,85856.710938,85666.648438,85669.906250,85646.382812</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:19</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>24</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>83831.000000,83777.750000,83786.703125,83764.984375,83677.765625,83675.765625,83670.765625,83626.375000,83609.460938,83566.539062,83564.257812,83572.234375,83562.562500,83534.937500,83552.359375,83530.226562,83542.187500,83521.445312,83498.585938,83462.031250,83487.367188,83479.187500,83448.882812,83390.515625</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>83672.359375,83765.000000,83730.804688,83777.875000,83758.320312,83702.195312,83525.468750,83592.968750,83577.421875,83608.515625,83519.546875,83540.679688,83443.945312,83555.437500,83479.703125,83417.281250,83450.953125,83417.132812,83529.960938,83356.164062,83400.937500,83388.367188,83365.703125,83316.390625</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>83251.070312,83147.101562,83082.890625,83023.562500,82902.625000,82810.117188,82767.875000,82674.421875,82558.828125,82436.070312,82357.078125,82300.851562,82244.125000,82104.031250,82016.070312,81963.273438,81855.976562,81823.617188,81557.015625,81409.789062,81365.312500,81336.406250,81197.828125,81037.484375</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>83529.679688,83404.000000,83376.054688,83339.132812,83182.320312,83147.148438,83116.054688,83058.148438,83036.109375,82947.382812,82834.476562,82836.484375,82833.820312,82701.085938,82685.398438,82686.046875,82552.539062,82519.320312,82384.992188,82332.695312,82270.523438,82131.234375,82045.703125,81957.914062</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3001,6 +3001,44 @@
       </c>
       <c r="F68" t="n">
         <v>83390.515625</v>
+      </c>
+      <c r="G68" t="n">
+        <v>84178.6328125</v>
+      </c>
+      <c r="H68" t="n">
+        <v>788.1171875</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.9362437487615853</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.7235614210680009</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:36</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>24</v>
+      </c>
+      <c r="F69" t="n">
+        <v>83959.875</v>
       </c>
     </row>
   </sheetData>
@@ -3014,7 +3052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7137,6 +7175,24 @@
           <t>83831.000000,83777.750000,83786.703125,83764.984375,83677.765625,83675.765625,83670.765625,83626.375000,83609.460938,83566.539062,83564.257812,83572.234375,83562.562500,83534.937500,83552.359375,83530.226562,83542.187500,83521.445312,83498.585938,83462.031250,83487.367188,83479.187500,83448.882812,83390.515625</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>83962.328125,84095.609375,84503.460938,83615.250000,83241.976562,83499.351562,83461.343750,83578.937500,84236.421875,83641.148438,84392.218750,84466.500000,84095.507812,84453.281250,84388.710938,84359.976562,84332.062500,84263.421875,84385.460938,84570.992188,84595.710938,84199.531250,84216.000000,84178.632812</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>131.328125,317.859375,716.757812,149.734375,435.789062,176.414062,209.421875,47.437500,626.960937,74.609376,827.960938,894.265625,532.945312,918.343750,836.351562,829.750001,789.875000,741.976563,886.874999,1108.960938,1108.343749,720.343750,767.117188,788.117188</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0.156413,0.377974,0.848199,0.179075,0.523521,0.211276,0.250921,0.056758,0.744287,0.089202,0.981087,1.058722,0.633738,1.087399,0.991070,0.983583,0.936625,0.880544,1.050981,1.311278,1.310165,0.855520,0.910892,0.936244</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0.7235614210680009</v>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>83672.359375,83765.000000,83730.804688,83777.875000,83758.320312,83702.195312,83525.468750,83592.968750,83577.421875,83608.515625,83519.546875,83540.679688,83443.945312,83555.437500,83479.703125,83417.281250,83450.953125,83417.132812,83529.960938,83356.164062,83400.937500,83388.367188,83365.703125,83316.390625</t>
@@ -7150,6 +7206,49 @@
       <c r="M68" t="inlineStr">
         <is>
           <t>83529.679688,83404.000000,83376.054688,83339.132812,83182.320312,83147.148438,83116.054688,83058.148438,83036.109375,82947.382812,82834.476562,82836.484375,82833.820312,82701.085938,82685.398438,82686.046875,82552.539062,82519.320312,82384.992188,82332.695312,82270.523438,82131.234375,82045.703125,81957.914062</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:36</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>24</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>84133.195312,84115.500000,84113.828125,84183.335938,84087.015625,84091.546875,84070.343750,84081.906250,84100.593750,84063.492188,84075.007812,84087.906250,84085.882812,84051.179688,84055.882812,84053.492188,84080.835938,84065.500000,84026.414062,83998.367188,83996.898438,84009.750000,83993.781250,83959.875000</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>83965.007812,84048.734375,84032.968750,84104.171875,84110.476562,84114.296875,83960.484375,84023.601562,84112.890625,84068.539062,84006.218750,84047.453125,83918.632812,84044.562500,84005.734375,83932.179688,83951.453125,83907.953125,84023.085938,83823.078125,83842.406250,83930.132812,83885.750000,83789.828125</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>83598.625000,83544.757812,83456.906250,83511.226562,83387.296875,83306.460938,83230.937500,83214.179688,83131.546875,83034.578125,83001.460938,82950.656250,82886.242188,82748.632812,82655.812500,82640.171875,82575.593750,82585.390625,82349.789062,82242.867188,82202.554688,82151.140625,82046.601562,81926.015625</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>83856.726562,83766.023438,83742.296875,83798.937500,83655.476562,83593.296875,83552.382812,83553.546875,83565.898438,83476.312500,83406.414062,83407.695312,83437.242188,83250.218750,83228.500000,83254.218750,83165.812500,83169.679688,83022.640625,82991.328125,82935.945312,82850.000000,82801.664062,82700.382812</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3039,6 +3039,44 @@
       </c>
       <c r="F69" t="n">
         <v>83959.875</v>
+      </c>
+      <c r="G69" t="n">
+        <v>83930.5625</v>
+      </c>
+      <c r="H69" t="n">
+        <v>29.3125</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.03492470338203679</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.2292896548656367</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:27</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>24</v>
+      </c>
+      <c r="F70" t="n">
+        <v>83792.1171875</v>
       </c>
     </row>
   </sheetData>
@@ -3052,7 +3090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7236,6 +7274,24 @@
           <t>84133.195312,84115.500000,84113.828125,84183.335938,84087.015625,84091.546875,84070.343750,84081.906250,84100.593750,84063.492188,84075.007812,84087.906250,84085.882812,84051.179688,84055.882812,84053.492188,84080.835938,84065.500000,84026.414062,83998.367188,83996.898438,84009.750000,83993.781250,83959.875000</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>84181.750000,84022.578125,84023.500000,84406.851562,84563.726562,84709.250000,84566.679688,84453.531250,83891.390625,84002.171875,83781.710938,83731.523438,83761.820312,83949.992188,84005.812500,83867.632812,83787.062500,84063.328125,84093.132812,83904.796875,84072.828125,83999.757812,83931.179688,83930.562500</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>48.554688,92.921875,90.328125,223.515624,476.710938,617.703125,496.335938,371.625000,209.203125,61.320313,293.296874,356.382812,324.062499,101.187501,50.070312,185.859376,293.773438,2.171875,66.718751,93.570313,75.929687,9.992188,62.601562,29.312500</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0.057678,0.110592,0.107503,0.264807,0.563730,0.729204,0.586917,0.440035,0.249374,0.072998,0.350073,0.425626,0.386886,0.120533,0.059603,0.221610,0.350619,0.002584,0.079339,0.111520,0.090314,0.011895,0.074587,0.034925</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0.2292896548656367</v>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>83965.007812,84048.734375,84032.968750,84104.171875,84110.476562,84114.296875,83960.484375,84023.601562,84112.890625,84068.539062,84006.218750,84047.453125,83918.632812,84044.562500,84005.734375,83932.179688,83951.453125,83907.953125,84023.085938,83823.078125,83842.406250,83930.132812,83885.750000,83789.828125</t>
@@ -7249,6 +7305,49 @@
       <c r="M69" t="inlineStr">
         <is>
           <t>83856.726562,83766.023438,83742.296875,83798.937500,83655.476562,83593.296875,83552.382812,83553.546875,83565.898438,83476.312500,83406.414062,83407.695312,83437.242188,83250.218750,83228.500000,83254.218750,83165.812500,83169.679688,83022.640625,82991.328125,82935.945312,82850.000000,82801.664062,82700.382812</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:27</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>24</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>83939.976562,83937.375000,83953.867188,83980.734375,83917.789062,83918.070312,83950.789062,83938.007812,83941.242188,83944.828125,83951.054688,83944.484375,83948.648438,83913.000000,83910.296875,83902.492188,83949.906250,83903.984375,83909.609375,83865.570312,83865.960938,83851.664062,83846.671875,83792.117188</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>83819.648438,83894.062500,83898.179688,83815.359375,83932.835938,83918.820312,83917.773438,83853.929688,83951.398438,83919.531250,83879.914062,83854.492188,83858.093750,83811.820312,83795.406250,83777.343750,83785.414062,83747.781250,83878.828125,83631.179688,83688.109375,83686.804688,83748.898438,83632.671875</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>83521.242188,83460.593750,83376.164062,83381.296875,83307.953125,83195.867188,83208.531250,83152.234375,83098.835938,83005.265625,82976.609375,82893.078125,82851.929688,82698.117188,82589.984375,82573.476562,82533.890625,82484.625000,82285.843750,82175.132812,82135.625000,82112.882812,82062.195312,81943.828125</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>83723.312500,83648.539062,83640.367188,83636.296875,83540.125000,83479.171875,83515.695312,83477.273438,83499.375000,83408.382812,83344.367188,83322.906250,83327.492188,83122.710938,83150.054688,83127.156250,83097.640625,83033.656250,82976.531250,82878.648438,82843.117188,82769.351562,82768.796875,82666.492188</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3077,6 +3077,44 @@
       </c>
       <c r="F70" t="n">
         <v>83792.1171875</v>
+      </c>
+      <c r="G70" t="n">
+        <v>84316.796875</v>
+      </c>
+      <c r="H70" t="n">
+        <v>524.6796875</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.6222718449300675</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.2835635578970028</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>24</v>
+      </c>
+      <c r="F71" t="n">
+        <v>84315.7265625</v>
       </c>
     </row>
   </sheetData>
@@ -3090,7 +3128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7335,6 +7373,24 @@
           <t>83939.976562,83937.375000,83953.867188,83980.734375,83917.789062,83918.070312,83950.789062,83938.007812,83941.242188,83944.828125,83951.054688,83944.484375,83948.648438,83913.000000,83910.296875,83902.492188,83949.906250,83903.984375,83909.609375,83865.570312,83865.960938,83851.664062,83846.671875,83792.117188</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>83918.351562,83882.648438,84103.921875,84194.906250,84004.796875,84171.546875,84161.007812,84053.781250,83931.867188,84014.562500,84146.859375,84104.296875,84126.640625,83994.609375,84000.250000,84016.328125,84137.617188,84266.359375,84421.437500,84291.210938,84471.476562,84435.343750,84375.312500,84316.796875</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>21.624999,54.726562,150.054687,214.171875,87.007813,253.476563,210.218751,115.773438,9.375001,69.734375,195.804687,159.812500,177.992187,81.609375,89.953125,113.835937,187.710938,362.375000,511.828125,425.640626,605.515624,583.679688,528.640625,524.679687</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0.025769,0.065242,0.178416,0.254376,0.103575,0.301143,0.249782,0.137737,0.011170,0.083003,0.232694,0.190017,0.211576,0.097160,0.107087,0.135493,0.223100,0.430035,0.606277,0.504964,0.716829,0.691274,0.626535,0.622272</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0.2835635578970028</v>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>83819.648438,83894.062500,83898.179688,83815.359375,83932.835938,83918.820312,83917.773438,83853.929688,83951.398438,83919.531250,83879.914062,83854.492188,83858.093750,83811.820312,83795.406250,83777.343750,83785.414062,83747.781250,83878.828125,83631.179688,83688.109375,83686.804688,83748.898438,83632.671875</t>
@@ -7348,6 +7404,49 @@
       <c r="M70" t="inlineStr">
         <is>
           <t>83723.312500,83648.539062,83640.367188,83636.296875,83540.125000,83479.171875,83515.695312,83477.273438,83499.375000,83408.382812,83344.367188,83322.906250,83327.492188,83122.710938,83150.054688,83127.156250,83097.640625,83033.656250,82976.531250,82878.648438,82843.117188,82769.351562,82768.796875,82666.492188</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>24</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>84355.351562,84338.804688,84356.328125,84402.148438,84353.500000,84339.078125,84396.812500,84370.515625,84348.164062,84376.601562,84406.484375,84381.296875,84382.429688,84366.945312,84383.281250,84391.171875,84387.125000,84383.195312,84373.062500,84382.851562,84368.679688,84370.500000,84359.742188,84315.726562</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>84339.421875,84304.031250,84314.031250,84259.445312,84398.164062,84299.507812,84303.125000,84259.562500,84364.796875,84331.164062,84328.695312,84253.539062,84251.820312,84238.132812,84249.289062,84220.546875,84321.101562,84250.484375,84300.726562,84140.429688,84182.203125,84204.601562,84273.421875,84168.312500</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>84095.921875,84056.828125,84005.718750,84073.687500,83942.687500,83863.296875,83906.929688,83818.265625,83699.437500,83675.765625,83678.796875,83545.421875,83462.031250,83402.273438,83325.789062,83314.953125,83248.039062,83224.625000,83008.937500,82936.562500,82910.015625,82916.281250,82904.210938,82818.585938</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>84228.218750,84179.210938,84173.523438,84187.984375,84119.078125,84034.937500,84115.117188,84054.250000,84063.156250,83966.695312,83958.453125,83919.039062,83926.289062,83794.796875,83808.523438,83812.281250,83797.421875,83718.781250,83660.914062,83592.765625,83556.328125,83533.195312,83541.062500,83460.515625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3115,6 +3115,44 @@
       </c>
       <c r="F71" t="n">
         <v>84315.7265625</v>
+      </c>
+      <c r="G71" t="n">
+        <v>83382.921875</v>
+      </c>
+      <c r="H71" t="n">
+        <v>932.8046875</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1.118699928623723</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.510099557080378</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:10</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>24</v>
+      </c>
+      <c r="F72" t="n">
+        <v>83326.0546875</v>
       </c>
     </row>
   </sheetData>
@@ -3128,7 +3166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7434,6 +7472,24 @@
           <t>84355.351562,84338.804688,84356.328125,84402.148438,84353.500000,84339.078125,84396.812500,84370.515625,84348.164062,84376.601562,84406.484375,84381.296875,84382.429688,84366.945312,84383.281250,84391.171875,84387.125000,84383.195312,84373.062500,84382.851562,84368.679688,84370.500000,84359.742188,84315.726562</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>84506.523438,84773.257812,84775.679688,84942.039062,84872.648438,84877.023438,84783.882812,85029.343750,84520.000000,84449.476562,84409.671875,84559.742188,84798.726562,84717.820312,84532.203125,84664.531250,84187.882812,84462.132812,84125.796875,83686.726562,83405.000000,83325.156250,83482.468750,83382.921875</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>151.171876,434.453124,419.351562,539.890624,519.148438,537.945312,387.070312,658.828125,171.835938,72.875001,3.187500,178.445312,416.296874,350.875001,148.921875,273.359375,199.242188,78.937501,247.265625,696.124999,963.679688,1045.343750,877.273438,932.804687</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0.178888,0.512488,0.494660,0.635599,0.611679,0.633794,0.456538,0.774824,0.203308,0.086294,0.003776,0.211029,0.490923,0.414169,0.176172,0.322874,0.236664,0.093459,0.293924,0.831822,1.155422,1.254536,1.050848,1.118700</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0.510099557080378</v>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>84339.421875,84304.031250,84314.031250,84259.445312,84398.164062,84299.507812,84303.125000,84259.562500,84364.796875,84331.164062,84328.695312,84253.539062,84251.820312,84238.132812,84249.289062,84220.546875,84321.101562,84250.484375,84300.726562,84140.429688,84182.203125,84204.601562,84273.421875,84168.312500</t>
@@ -7447,6 +7503,49 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>84228.218750,84179.210938,84173.523438,84187.984375,84119.078125,84034.937500,84115.117188,84054.250000,84063.156250,83966.695312,83958.453125,83919.039062,83926.289062,83794.796875,83808.523438,83812.281250,83797.421875,83718.781250,83660.914062,83592.765625,83556.328125,83533.195312,83541.062500,83460.515625</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:10</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>24</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>83325.765625,83310.523438,83286.992188,83301.210938,83242.367188,83255.304688,83314.468750,83284.585938,83250.304688,83302.968750,83309.242188,83306.976562,83340.046875,83338.281250,83397.171875,83372.656250,83393.445312,83408.343750,83371.968750,83383.390625,83350.812500,83356.273438,83363.500000,83326.054688</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>83288.843750,83324.296875,83327.421875,83279.140625,83374.640625,83354.757812,83401.976562,83205.773438,83338.835938,83306.632812,83346.093750,83359.609375,83252.851562,83404.375000,83336.234375,83348.015625,83394.859375,83418.679688,83442.187500,83322.750000,83281.054688,83239.335938,83446.195312,83306.000000</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>82976.039062,82939.351562,82840.945312,82794.789062,82663.914062,82621.312500,82643.851562,82542.054688,82427.648438,82383.023438,82336.390625,82288.921875,82278.546875,82219.601562,82213.796875,82166.085938,82130.703125,82145.476562,81878.476562,81849.437500,81798.265625,81750.351562,81761.140625,81663.031250</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>83138.398438,83093.585938,83020.671875,82969.023438,82854.515625,82828.679688,82887.859375,82795.226562,82816.789062,82732.593750,82690.226562,82719.687500,82717.203125,82588.375000,82697.539062,82655.781250,82670.312500,82603.218750,82543.765625,82514.492188,82438.578125,82383.695312,82379.875000,82295.132812</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3153,6 +3153,44 @@
       </c>
       <c r="F72" t="n">
         <v>83326.0546875</v>
+      </c>
+      <c r="G72" t="n">
+        <v>83281.328125</v>
+      </c>
+      <c r="H72" t="n">
+        <v>44.7265625</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.05370539052027155</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.3354511514831796</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:28:55</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>24</v>
+      </c>
+      <c r="F73" t="n">
+        <v>83368.3046875</v>
       </c>
     </row>
   </sheetData>
@@ -3166,7 +3204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7533,6 +7571,24 @@
           <t>83325.765625,83310.523438,83286.992188,83301.210938,83242.367188,83255.304688,83314.468750,83284.585938,83250.304688,83302.968750,83309.242188,83306.976562,83340.046875,83338.281250,83397.171875,83372.656250,83393.445312,83408.343750,83371.968750,83383.390625,83350.812500,83356.273438,83363.500000,83326.054688</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>83134.007812,82912.039062,82913.578125,82624.179688,82908.132812,83058.929688,83539.023438,83629.890625,82988.632812,83365.789062,83677.390625,83846.953125,84017.421875,83364.843750,83501.476562,83181.031250,83513.289062,83456.742188,83146.476562,83024.781250,82930.046875,83038.382812,83170.562500,83281.328125</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>191.757812,398.484376,373.414063,677.031251,334.234376,196.375001,224.554688,345.304687,261.671876,62.820312,368.148437,539.976563,677.375000,26.562500,104.304688,191.625000,119.843751,48.398438,225.492188,358.609375,420.765625,317.890626,192.937500,44.726563</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0.230661,0.480611,0.450365,0.819411,0.403138,0.236429,0.268802,0.412896,0.315311,0.075355,0.439962,0.644003,0.806232,0.031863,0.124914,0.230371,0.143503,0.057992,0.271199,0.431931,0.507374,0.382824,0.231978,0.053705</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0.3354511514831796</v>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>83288.843750,83324.296875,83327.421875,83279.140625,83374.640625,83354.757812,83401.976562,83205.773438,83338.835938,83306.632812,83346.093750,83359.609375,83252.851562,83404.375000,83336.234375,83348.015625,83394.859375,83418.679688,83442.187500,83322.750000,83281.054688,83239.335938,83446.195312,83306.000000</t>
@@ -7546,6 +7602,49 @@
       <c r="M72" t="inlineStr">
         <is>
           <t>83138.398438,83093.585938,83020.671875,82969.023438,82854.515625,82828.679688,82887.859375,82795.226562,82816.789062,82732.593750,82690.226562,82719.687500,82717.203125,82588.375000,82697.539062,82655.781250,82670.312500,82603.218750,82543.765625,82514.492188,82438.578125,82383.695312,82379.875000,82295.132812</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:28:55</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>24</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>83236.515625,83237.460938,83253.609375,83286.007812,83306.742188,83323.625000,83367.273438,83346.500000,83324.046875,83381.062500,83375.218750,83367.484375,83420.796875,83387.859375,83394.031250,83387.234375,83389.742188,83371.664062,83368.726562,83408.789062,83360.406250,83358.953125,83366.210938,83368.304688</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>83257.742188,83287.921875,83285.562500,83256.578125,83369.367188,83433.601562,83437.835938,83327.835938,83350.625000,83405.445312,83392.007812,83433.820312,83367.664062,83436.937500,83416.828125,83352.398438,83346.656250,83355.304688,83451.968750,83289.039062,83299.781250,83260.820312,83408.109375,83339.117188</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>82916.226562,82868.132812,82798.320312,82810.101562,82772.859375,82719.554688,82730.898438,82640.117188,82574.765625,82560.398438,82544.421875,82499.117188,82488.570312,82388.976562,82404.640625,82324.804688,82284.867188,82249.023438,82045.828125,82063.500000,82006.085938,81969.898438,81939.140625,81889.335938</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>83046.406250,82994.351562,82965.640625,82952.992188,82925.765625,82901.718750,82948.765625,82890.429688,82905.578125,82861.601562,82822.195312,82864.867188,82888.109375,82733.500000,82815.414062,82783.640625,82716.445312,82639.898438,82608.398438,82628.007812,82547.390625,82502.906250,82514.164062,82483.687500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3191,6 +3191,44 @@
       </c>
       <c r="F73" t="n">
         <v>83368.3046875</v>
+      </c>
+      <c r="G73" t="n">
+        <v>83150.8984375</v>
+      </c>
+      <c r="H73" t="n">
+        <v>217.40625</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.2614598928999095</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.47123739043947</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:31</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>24</v>
+      </c>
+      <c r="F74" t="n">
+        <v>83041.1640625</v>
       </c>
     </row>
   </sheetData>
@@ -3204,7 +3242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7632,6 +7670,24 @@
           <t>83236.515625,83237.460938,83253.609375,83286.007812,83306.742188,83323.625000,83367.273438,83346.500000,83324.046875,83381.062500,83375.218750,83367.484375,83420.796875,83387.859375,83394.031250,83387.234375,83389.742188,83371.664062,83368.726562,83408.789062,83360.406250,83358.953125,83366.210938,83368.304688</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>83976.007812,83948.132812,83845.921875,84221.328125,84000.906250,84324.031250,84309.210938,84186.218750,83717.421875,83041.390625,83034.929688,83055.421875,83609.976562,83549.007812,83582.671875,83473.882812,83578.828125,83638.406250,83418.281250,83404.773438,83347.671875,83269.156250,83174.046875,83150.898438</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>739.492188,710.671874,592.312500,935.320313,694.164062,1000.406250,941.937499,839.718750,393.375000,339.671875,340.289062,312.062500,189.179688,161.148438,188.640625,86.648438,189.085937,266.742188,49.554688,4.015624,12.734375,89.796875,192.164063,217.406251</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>0.880599,0.846561,0.706430,1.110550,0.826377,1.186383,1.117242,0.997454,0.469884,0.409039,0.409814,0.375728,0.226264,0.192879,0.225693,0.103803,0.226237,0.318923,0.059405,0.004815,0.015279,0.107839,0.231038,0.261460</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.47123739043947</v>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>83257.742188,83287.921875,83285.562500,83256.578125,83369.367188,83433.601562,83437.835938,83327.835938,83350.625000,83405.445312,83392.007812,83433.820312,83367.664062,83436.937500,83416.828125,83352.398438,83346.656250,83355.304688,83451.968750,83289.039062,83299.781250,83260.820312,83408.109375,83339.117188</t>
@@ -7645,6 +7701,49 @@
       <c r="M73" t="inlineStr">
         <is>
           <t>83046.406250,82994.351562,82965.640625,82952.992188,82925.765625,82901.718750,82948.765625,82890.429688,82905.578125,82861.601562,82822.195312,82864.867188,82888.109375,82733.500000,82815.414062,82783.640625,82716.445312,82639.898438,82608.398438,82628.007812,82547.390625,82502.906250,82514.164062,82483.687500</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:31</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>24</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>83136.000000,83113.257812,83116.078125,83114.023438,83095.992188,83116.835938,83132.882812,83089.726562,83046.210938,83078.414062,83046.632812,83051.171875,83073.492188,83047.335938,83063.898438,83065.687500,83077.914062,83063.218750,83076.078125,83113.367188,83082.953125,83049.414062,83017.296875,83041.164062</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>83134.523438,83211.468750,83131.695312,83118.773438,83133.781250,83189.625000,83211.695312,83000.156250,83075.539062,83104.523438,83055.359375,83081.500000,83042.906250,83118.992188,83062.875000,83015.773438,83083.835938,83083.367188,83176.109375,83000.898438,83001.625000,82945.734375,83089.984375,83020.632812</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>82790.453125,82721.398438,82645.921875,82626.367188,82523.265625,82494.804688,82484.117188,82376.132812,82279.250000,82257.281250,82194.210938,82128.781250,82085.648438,82022.890625,82035.718750,81967.492188,81950.867188,81901.773438,81735.953125,81746.828125,81699.664062,81631.265625,81586.562500,81579.710938</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>82945.367188,82873.023438,82829.390625,82794.914062,82718.695312,82713.023438,82726.914062,82653.539062,82643.375000,82564.875000,82491.625000,82515.796875,82518.843750,82417.570312,82466.328125,82441.539062,82441.234375,82336.265625,82324.500000,82324.609375,82258.781250,82177.156250,82147.148438,82178.835938</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3229,6 +3229,44 @@
       </c>
       <c r="F74" t="n">
         <v>83041.1640625</v>
+      </c>
+      <c r="G74" t="n">
+        <v>84217.28125</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1176.1171875</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1.396527137950087</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.8662893957455136</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:40</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="n">
+        <v>83980.9921875</v>
       </c>
     </row>
   </sheetData>
@@ -3242,7 +3280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7731,6 +7769,24 @@
           <t>83136.000000,83113.257812,83116.078125,83114.023438,83095.992188,83116.835938,83132.882812,83089.726562,83046.210938,83078.414062,83046.632812,83051.171875,83073.492188,83047.335938,83063.898438,83065.687500,83077.914062,83063.218750,83076.078125,83113.367188,83082.953125,83049.414062,83017.296875,83041.164062</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>83005.882812,83271.382812,83023.148438,83598.187500,83883.359375,83879.007812,85258.070312,84579.820312,83754.468750,84078.968750,84299.851562,84007.812500,83911.906250,83558.976562,83617.757812,83712.593750,83625.148438,83556.148438,83455.890625,83459.609375,83444.132812,83695.539062,84049.593750,84217.281250</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>130.117188,158.125001,92.929688,484.164062,787.367187,762.171874,2125.187501,1490.093751,708.257812,1000.554688,1253.218751,956.640625,838.414062,511.640624,553.859374,646.906250,547.234376,492.929688,379.812500,346.242187,361.179688,646.125001,1032.296875,1176.117188</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0.156757,0.189891,0.111932,0.579156,0.938645,0.908656,2.492653,1.761760,0.845636,1.190018,1.486620,1.138752,0.999160,0.612311,0.662371,0.772771,0.654390,0.589938,0.455106,0.414862,0.432840,0.771995,1.228200,1.396527</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.8662893957455136</v>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>83134.523438,83211.468750,83131.695312,83118.773438,83133.781250,83189.625000,83211.695312,83000.156250,83075.539062,83104.523438,83055.359375,83081.500000,83042.906250,83118.992188,83062.875000,83015.773438,83083.835938,83083.367188,83176.109375,83000.898438,83001.625000,82945.734375,83089.984375,83020.632812</t>
@@ -7744,6 +7800,49 @@
       <c r="M74" t="inlineStr">
         <is>
           <t>82945.367188,82873.023438,82829.390625,82794.914062,82718.695312,82713.023438,82726.914062,82653.539062,82643.375000,82564.875000,82491.625000,82515.796875,82518.843750,82417.570312,82466.328125,82441.539062,82441.234375,82336.265625,82324.500000,82324.609375,82258.781250,82177.156250,82147.148438,82178.835938</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:40</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>84205.140625,84181.320312,84164.914062,84163.273438,84170.679688,84181.234375,84187.562500,84127.648438,84122.578125,84150.437500,84090.671875,84084.546875,84072.312500,84044.429688,84067.867188,84031.843750,84073.367188,84037.445312,84033.468750,84044.460938,84023.210938,83972.632812,83952.781250,83980.992188</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>84189.687500,84252.250000,84140.351562,84163.875000,84155.429688,84173.875000,84206.906250,84096.140625,84116.242188,84145.460938,84062.218750,84062.773438,84017.242188,84054.921875,84017.718750,83992.921875,84007.054688,83995.078125,84075.421875,83941.359375,83904.757812,83925.437500,83992.218750,83935.031250</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>83779.804688,83683.929688,83582.750000,83539.460938,83475.335938,83439.242188,83405.195312,83264.992188,83242.390625,83219.203125,83151.960938,83078.851562,83038.117188,82965.523438,82995.023438,82867.140625,82892.648438,82845.523438,82708.710938,82668.125000,82637.453125,82565.906250,82505.351562,82517.054688</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>83981.164062,83887.703125,83817.601562,83798.742188,83724.382812,83681.648438,83684.210938,83573.937500,83598.484375,83545.304688,83462.273438,83461.570312,83459.351562,83364.507812,83410.117188,83342.226562,83376.726562,83298.734375,83260.242188,83242.609375,83186.500000,83095.539062,83075.570312,83088.421875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3267,6 +3267,44 @@
       </c>
       <c r="F75" t="n">
         <v>83980.9921875</v>
+      </c>
+      <c r="G75" t="n">
+        <v>86493.828125</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2512.8359375</v>
+      </c>
+      <c r="I75" t="n">
+        <v>2.905219935309691</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.85284651443354</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:15</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>24</v>
+      </c>
+      <c r="F76" t="n">
+        <v>85893.6640625</v>
       </c>
     </row>
   </sheetData>
@@ -3280,7 +3318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7830,6 +7868,24 @@
           <t>84205.140625,84181.320312,84164.914062,84163.273438,84170.679688,84181.234375,84187.562500,84127.648438,84122.578125,84150.437500,84090.671875,84084.546875,84072.312500,84044.429688,84067.867188,84031.843750,84073.367188,84037.445312,84033.468750,84044.460938,84023.210938,83972.632812,83952.781250,83980.992188</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>84076.257812,83371.843750,83519.460938,83744.476562,83922.062500,83882.023438,83706.460938,83925.406250,84022.726562,84130.062500,84164.703125,84872.046875,84767.851562,84644.929688,84607.078125,84529.218750,84719.218750,84848.726562,84762.750000,84883.750000,85165.742188,85485.812500,86641.687500,86493.828125</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>128.882812,809.476562,645.453124,418.796876,248.617188,299.210938,481.101562,202.242188,99.851562,20.375000,74.031250,787.500000,695.539062,600.499999,539.210937,497.375000,645.851562,811.281251,729.281250,839.289062,1142.531249,1513.179688,2688.906250,2512.835937</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0.153293,0.970923,0.772818,0.500089,0.296248,0.356704,0.574748,0.240979,0.118839,0.024218,0.087960,0.927867,0.820522,0.709434,0.637312,0.588406,0.762344,0.956150,0.860379,0.988751,1.341539,1.770095,3.103479,2.905220</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0.85284651443354</v>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>84189.687500,84252.250000,84140.351562,84163.875000,84155.429688,84173.875000,84206.906250,84096.140625,84116.242188,84145.460938,84062.218750,84062.773438,84017.242188,84054.921875,84017.718750,83992.921875,84007.054688,83995.078125,84075.421875,83941.359375,83904.757812,83925.437500,83992.218750,83935.031250</t>
@@ -7843,6 +7899,49 @@
       <c r="M75" t="inlineStr">
         <is>
           <t>83981.164062,83887.703125,83817.601562,83798.742188,83724.382812,83681.648438,83684.210938,83573.937500,83598.484375,83545.304688,83462.273438,83461.570312,83459.351562,83364.507812,83410.117188,83342.226562,83376.726562,83298.734375,83260.242188,83242.609375,83186.500000,83095.539062,83075.570312,83088.421875</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:15</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>24</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>86351.054688,86337.414062,86331.015625,86322.492188,86285.164062,86255.273438,86257.468750,86180.046875,86184.554688,86180.460938,86166.906250,86122.851562,86103.640625,86018.500000,86056.351562,85994.882812,86030.164062,85970.515625,85933.585938,85927.546875,85890.609375,85884.460938,85884.656250,85893.664062</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>86335.132812,86301.929688,86338.664062,86312.320312,86184.257812,86230.656250,86219.921875,86184.851562,86149.953125,86180.265625,86173.523438,86051.953125,85955.226562,85990.390625,85939.718750,85981.500000,85906.632812,85861.718750,85958.507812,85909.640625,85849.312500,85836.687500,85895.789062,85861.523438</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>85646.898438,85501.234375,85365.406250,85297.507812,85160.703125,85052.687500,84995.109375,84848.015625,84824.906250,84751.226562,84700.695312,84598.335938,84625.343750,84483.468750,84456.257812,84401.703125,84389.796875,84358.593750,84174.812500,84132.062500,84091.078125,84043.429688,84048.406250,84069.296875</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>85957.289062,85844.148438,85750.226562,85724.273438,85590.304688,85507.203125,85480.476562,85338.312500,85397.851562,85316.234375,85250.375000,85210.546875,85180.515625,85024.398438,85058.132812,85015.031250,85038.804688,84940.367188,84836.875000,84824.453125,84750.375000,84724.023438,84726.390625,84737.992188</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3305,6 +3305,44 @@
       </c>
       <c r="F76" t="n">
         <v>85893.6640625</v>
+      </c>
+      <c r="G76" t="n">
+        <v>84538.0078125</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1355.65625</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1.603605626722078</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1.132490801141953</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:02:05</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>24</v>
+      </c>
+      <c r="F77" t="n">
+        <v>84403.25</v>
       </c>
     </row>
   </sheetData>
@@ -3318,7 +3356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7929,6 +7967,24 @@
           <t>86351.054688,86337.414062,86331.015625,86322.492188,86285.164062,86255.273438,86257.468750,86180.046875,86184.554688,86180.460938,86166.906250,86122.851562,86103.640625,86018.500000,86056.351562,85994.882812,86030.164062,85970.515625,85933.585938,85927.546875,85890.609375,85884.460938,85884.656250,85893.664062</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>85964.367188,86088.507812,86235.648438,86352.273438,86281.000000,86412.210938,86811.281250,86579.007812,85671.828125,85316.351562,85143.500000,84776.093750,84240.843750,84291.492188,84430.546875,84512.601562,84549.578125,84504.882812,84638.718750,84628.148438,84585.031250,84681.000000,84573.843750,84538.007812</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>386.687501,248.906249,95.367188,29.781249,4.164062,156.937499,553.812500,398.960938,512.726563,864.109376,1023.406250,1346.757812,1862.796875,1727.007812,1625.804687,1482.281249,1480.585937,1465.632812,1294.867188,1299.398438,1305.578125,1203.460938,1310.812500,1355.656249</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>0.449823,0.289128,0.110589,0.034488,0.004826,0.181615,0.637950,0.460806,0.598477,1.012830,1.201978,1.588606,2.211275,2.048852,1.925612,1.753917,1.751145,1.734376,1.529876,1.535421,1.543510,1.421170,1.549903,1.603606</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>1.132490801141953</v>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>86335.132812,86301.929688,86338.664062,86312.320312,86184.257812,86230.656250,86219.921875,86184.851562,86149.953125,86180.265625,86173.523438,86051.953125,85955.226562,85990.390625,85939.718750,85981.500000,85906.632812,85861.718750,85958.507812,85909.640625,85849.312500,85836.687500,85895.789062,85861.523438</t>
@@ -7942,6 +7998,49 @@
       <c r="M76" t="inlineStr">
         <is>
           <t>85957.289062,85844.148438,85750.226562,85724.273438,85590.304688,85507.203125,85480.476562,85338.312500,85397.851562,85316.234375,85250.375000,85210.546875,85180.515625,85024.398438,85058.132812,85015.031250,85038.804688,84940.367188,84836.875000,84824.453125,84750.375000,84724.023438,84726.390625,84737.992188</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:02:05</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>24</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>84555.609375,84536.320312,84537.171875,84556.609375,84527.289062,84497.367188,84487.992188,84459.343750,84464.085938,84432.328125,84405.640625,84409.609375,84388.070312,84371.351562,84398.140625,84384.117188,84398.562500,84387.140625,84404.156250,84389.898438,84395.015625,84404.289062,84391.664062,84403.250000</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>84519.835938,84584.859375,84512.367188,84535.570312,84517.421875,84512.523438,84470.718750,84435.515625,84460.500000,84452.148438,84435.101562,84339.179688,84323.984375,84365.992188,84319.367188,84362.984375,84316.679688,84363.304688,84410.242188,84369.250000,84360.234375,84323.640625,84390.765625,84347.578125</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>84186.898438,84125.765625,84069.375000,84074.023438,83949.750000,83857.867188,83825.007812,83749.117188,83688.992188,83591.226562,83504.828125,83497.695312,83431.843750,83364.781250,83311.812500,83266.171875,83252.960938,83238.789062,83152.070312,83073.820312,83106.507812,83063.265625,83037.460938,83037.226562</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>84365.609375,84289.257812,84256.812500,84248.515625,84182.609375,84100.359375,84069.585938,83989.421875,84048.382812,83950.140625,83862.218750,83853.070312,83822.898438,83774.171875,83765.625000,83751.195312,83753.781250,83705.156250,83668.484375,83673.203125,83664.625000,83617.281250,83585.515625,83603.929688</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,6 +3343,44 @@
       </c>
       <c r="F77" t="n">
         <v>84403.25</v>
+      </c>
+      <c r="G77" t="n">
+        <v>84854.546875</v>
+      </c>
+      <c r="H77" t="n">
+        <v>451.296875</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.5318476046602542</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.384448063980397</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:28</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>24</v>
+      </c>
+      <c r="F78" t="n">
+        <v>84809.65625</v>
       </c>
     </row>
   </sheetData>
@@ -3356,7 +3394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8028,6 +8066,24 @@
           <t>84555.609375,84536.320312,84537.171875,84556.609375,84527.289062,84497.367188,84487.992188,84459.343750,84464.085938,84432.328125,84405.640625,84409.609375,84388.070312,84371.351562,84398.140625,84384.117188,84398.562500,84387.140625,84404.156250,84389.898438,84395.015625,84404.289062,84391.664062,84403.250000</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>84554.062500,84552.148438,84593.101562,84583.320312,84621.062500,84661.851562,84864.773438,84857.437500,84842.992188,84862.156250,84853.132812,84990.968750,84933.648438,84836.992188,84739.203125,84708.570312,84755.937500,84742.218750,84786.468750,84794.476562,84790.046875,84824.359375,84805.007812,84854.546875</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>1.546875,15.828126,55.929688,26.710938,93.773438,164.484374,376.781249,398.093750,378.906249,429.828125,447.492188,581.359375,545.578126,465.640626,341.062500,324.453124,357.375000,355.078125,382.312500,404.578124,395.031250,420.070313,413.343751,451.296875</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>0.001829,0.018720,0.066116,0.031579,0.110816,0.194284,0.443978,0.469132,0.446597,0.506502,0.527373,0.684025,0.642358,0.548865,0.402485,0.383023,0.421652,0.419010,0.450912,0.477128,0.465893,0.495224,0.487405,0.531848</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0.384448063980397</v>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>84519.835938,84584.859375,84512.367188,84535.570312,84517.421875,84512.523438,84470.718750,84435.515625,84460.500000,84452.148438,84435.101562,84339.179688,84323.984375,84365.992188,84319.367188,84362.984375,84316.679688,84363.304688,84410.242188,84369.250000,84360.234375,84323.640625,84390.765625,84347.578125</t>
@@ -8041,6 +8097,49 @@
       <c r="M77" t="inlineStr">
         <is>
           <t>84365.609375,84289.257812,84256.812500,84248.515625,84182.609375,84100.359375,84069.585938,83989.421875,84048.382812,83950.140625,83862.218750,83853.070312,83822.898438,83774.171875,83765.625000,83751.195312,83753.781250,83705.156250,83668.484375,83673.203125,83664.625000,83617.281250,83585.515625,83603.929688</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:28</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>24</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>84849.921875,84837.328125,84858.148438,84893.265625,84889.156250,84893.203125,84905.367188,84892.390625,84903.062500,84903.898438,84900.234375,84904.117188,84876.007812,84853.757812,84861.945312,84852.375000,84851.984375,84819.132812,84828.421875,84822.960938,84837.882812,84813.492188,84806.945312,84809.656250</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>84822.859375,84869.140625,84823.132812,84884.492188,84895.140625,84892.617188,84883.335938,84884.375000,84872.648438,84866.015625,84857.304688,84837.820312,84810.875000,84853.273438,84795.398438,84782.859375,84770.015625,84749.117188,84812.406250,84715.851562,84755.250000,84696.218750,84733.843750,84764.320312</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>84613.648438,84590.539062,84559.851562,84609.132812,84525.390625,84471.351562,84462.796875,84390.054688,84331.789062,84262.054688,84221.390625,84187.273438,84089.562500,84044.781250,83993.546875,83932.000000,83890.250000,83824.093750,83711.273438,83675.562500,83670.687500,83593.500000,83572.929688,83549.843750</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>84743.679688,84697.789062,84695.484375,84722.984375,84680.531250,84649.671875,84651.046875,84608.125000,84632.203125,84579.828125,84513.398438,84505.640625,84460.593750,84388.156250,84387.218750,84370.492188,84340.242188,84252.765625,84214.789062,84222.414062,84208.765625,84117.335938,84110.539062,84121.484375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3381,6 +3381,44 @@
       </c>
       <c r="F78" t="n">
         <v>84809.65625</v>
+      </c>
+      <c r="G78" t="n">
+        <v>85488.0234375</v>
+      </c>
+      <c r="H78" t="n">
+        <v>678.3671875</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.7935230693407619</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.8713344047164647</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:11</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>24</v>
+      </c>
+      <c r="F79" t="n">
+        <v>85136.25</v>
       </c>
     </row>
   </sheetData>
@@ -3394,7 +3432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8127,6 +8165,24 @@
           <t>84849.921875,84837.328125,84858.148438,84893.265625,84889.156250,84893.203125,84905.367188,84892.390625,84903.062500,84903.898438,84900.234375,84904.117188,84876.007812,84853.757812,84861.945312,84852.375000,84851.984375,84819.132812,84828.421875,84822.960938,84837.882812,84813.492188,84806.945312,84809.656250</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>85013.210938,85092.992188,85093.796875,85219.398438,85260.250000,85304.171875,85127.359375,85233.867188,85276.359375,85244.976562,85358.312500,85302.890625,85325.078125,85417.468750,85812.031250,85845.960938,86423.000000,86512.976562,86632.007812,86596.906250,86509.656250,86052.296875,85505.437500,85488.023438</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>163.289062,255.664062,235.648437,326.132812,371.093750,410.968750,221.992187,341.476562,373.296875,341.078124,458.078125,398.773437,449.070313,563.710938,950.085938,993.585938,1571.015625,1693.843751,1803.585938,1773.945312,1671.773438,1238.804687,698.492188,678.367188</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0.192075,0.300453,0.276928,0.382698,0.435248,0.481769,0.260777,0.400635,0.437750,0.400115,0.536653,0.467479,0.526305,0.659948,1.107171,1.157406,1.817821,1.957907,2.081893,2.048509,1.932470,1.439595,0.816898,0.793523</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0.8713344047164647</v>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>84822.859375,84869.140625,84823.132812,84884.492188,84895.140625,84892.617188,84883.335938,84884.375000,84872.648438,84866.015625,84857.304688,84837.820312,84810.875000,84853.273438,84795.398438,84782.859375,84770.015625,84749.117188,84812.406250,84715.851562,84755.250000,84696.218750,84733.843750,84764.320312</t>
@@ -8140,6 +8196,49 @@
       <c r="M78" t="inlineStr">
         <is>
           <t>84743.679688,84697.789062,84695.484375,84722.984375,84680.531250,84649.671875,84651.046875,84608.125000,84632.203125,84579.828125,84513.398438,84505.640625,84460.593750,84388.156250,84387.218750,84370.492188,84340.242188,84252.765625,84214.789062,84222.414062,84208.765625,84117.335938,84110.539062,84121.484375</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:11</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>24</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>85437.789062,85376.796875,85354.523438,85353.562500,85294.484375,85282.375000,85278.554688,85258.320312,85257.960938,85272.898438,85246.554688,85265.523438,85222.734375,85202.828125,85238.906250,85251.218750,85253.023438,85230.343750,85223.078125,85211.234375,85225.914062,85196.968750,85145.335938,85136.250000</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>85360.859375,85395.015625,85295.898438,85330.406250,85316.406250,85209.164062,85224.343750,85224.585938,85151.179688,85238.976562,85179.820312,85097.242188,85056.968750,85133.265625,85101.523438,85075.601562,85092.773438,85022.976562,85083.335938,85039.734375,85097.781250,85079.132812,84943.539062,84993.039062</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>85092.554688,84980.203125,84858.843750,84818.367188,84656.445312,84575.593750,84505.671875,84422.710938,84338.453125,84253.453125,84171.796875,84156.226562,84077.421875,83997.210938,83955.718750,83910.609375,83898.765625,83824.289062,83715.187500,83631.117188,83625.015625,83562.546875,83523.585938,83488.218750</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>85262.570312,85141.046875,85075.039062,85029.609375,84920.476562,84848.265625,84806.046875,84732.453125,84736.421875,84674.289062,84593.843750,84591.367188,84533.460938,84460.765625,84472.265625,84477.265625,84481.101562,84384.703125,84350.296875,84316.843750,84314.109375,84223.445312,84206.234375,84192.609375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3419,6 +3419,44 @@
       </c>
       <c r="F79" t="n">
         <v>85136.25</v>
+      </c>
+      <c r="G79" t="n">
+        <v>85496.5234375</v>
+      </c>
+      <c r="H79" t="n">
+        <v>360.2734375</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.4213895758736535</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.632192267834232</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:19</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>24</v>
+      </c>
+      <c r="F80" t="n">
+        <v>85277.9609375</v>
       </c>
     </row>
   </sheetData>
@@ -3432,7 +3470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8226,6 +8264,24 @@
           <t>85437.789062,85376.796875,85354.523438,85353.562500,85294.484375,85282.375000,85278.554688,85258.320312,85257.960938,85272.898438,85246.554688,85265.523438,85222.734375,85202.828125,85238.906250,85251.218750,85253.023438,85230.343750,85223.078125,85211.234375,85225.914062,85196.968750,85145.335938,85136.250000</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>86230.117188,86235.281250,86190.656250,85961.328125,86102.617188,86197.921875,85870.273438,86435.953125,85623.031250,85251.546875,85296.046875,85428.187500,85658.320312,85724.546875,85772.078125,85941.273438,85929.398438,85748.953125,85901.968750,85613.328125,85525.109375,85476.140625,85605.593750,85496.523438</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>792.328126,858.484375,836.132812,607.765625,808.132812,915.546875,591.718749,1177.632813,365.070312,21.351563,49.492187,162.664062,435.585938,521.718750,533.171875,690.054688,676.374999,518.609375,678.890625,402.093750,299.195313,279.171875,460.257812,360.273438</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>0.918853,0.995514,0.970097,0.707022,0.938569,1.062145,0.689085,1.362434,0.426369,0.025045,0.058024,0.190410,0.508516,0.608599,0.621615,0.802937,0.787129,0.604800,0.790309,0.469663,0.349833,0.326608,0.537649,0.421390</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0.632192267834232</v>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>85360.859375,85395.015625,85295.898438,85330.406250,85316.406250,85209.164062,85224.343750,85224.585938,85151.179688,85238.976562,85179.820312,85097.242188,85056.968750,85133.265625,85101.523438,85075.601562,85092.773438,85022.976562,85083.335938,85039.734375,85097.781250,85079.132812,84943.539062,84993.039062</t>
@@ -8239,6 +8295,49 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>85262.570312,85141.046875,85075.039062,85029.609375,84920.476562,84848.265625,84806.046875,84732.453125,84736.421875,84674.289062,84593.843750,84591.367188,84533.460938,84460.765625,84472.265625,84477.265625,84481.101562,84384.703125,84350.296875,84316.843750,84314.109375,84223.445312,84206.234375,84192.609375</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:19</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>24</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>85412.992188,85378.109375,85365.625000,85382.851562,85341.460938,85353.070312,85352.195312,85338.273438,85348.460938,85332.257812,85311.328125,85332.632812,85301.234375,85294.328125,85323.687500,85333.648438,85355.046875,85328.390625,85317.484375,85326.125000,85344.109375,85318.539062,85274.078125,85277.960938</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>85353.156250,85382.265625,85308.132812,85364.531250,85408.937500,85336.945312,85322.687500,85287.218750,85267.375000,85272.859375,85264.859375,85216.343750,85157.804688,85283.773438,85233.007812,85203.179688,85227.648438,85166.968750,85260.117188,85136.859375,85220.953125,85210.031250,85147.265625,85150.289062</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>85078.718750,85009.062500,84925.015625,84919.812500,84819.492188,84759.320312,84736.500000,84641.281250,84575.226562,84480.960938,84420.531250,84421.539062,84338.804688,84288.648438,84246.054688,84214.335938,84201.953125,84157.765625,84037.812500,83984.585938,83993.093750,83964.765625,83902.640625,83886.281250</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>85229.210938,85140.296875,85103.109375,85089.312500,85022.687500,84979.375000,84973.320312,84911.109375,84923.335938,84844.226562,84772.593750,84792.640625,84747.984375,84695.671875,84703.093750,84708.093750,84695.625000,84620.875000,84587.250000,84590.140625,84596.171875,84522.031250,84490.781250,84481.414062</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3457,6 +3457,44 @@
       </c>
       <c r="F80" t="n">
         <v>85277.9609375</v>
+      </c>
+      <c r="G80" t="n">
+        <v>84171.6171875</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1106.34375</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1.314390511869955</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.7742567298217934</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:30</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>24</v>
+      </c>
+      <c r="F81" t="n">
+        <v>84176.5390625</v>
       </c>
     </row>
   </sheetData>
@@ -3470,7 +3508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8325,6 +8363,24 @@
           <t>85412.992188,85378.109375,85365.625000,85382.851562,85341.460938,85353.070312,85352.195312,85338.273438,85348.460938,85332.257812,85311.328125,85332.632812,85301.234375,85294.328125,85323.687500,85333.648438,85355.046875,85328.390625,85317.484375,85326.125000,85344.109375,85318.539062,85274.078125,85277.960938</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>85539.531250,86003.570312,85971.851562,86139.953125,86236.187500,86193.757812,86306.929688,86600.023438,85710.000000,85576.093750,85719.367188,85494.000000,85610.000000,85607.578125,85614.656250,85527.218750,85547.773438,85535.492188,84391.421875,83847.562500,84122.523438,84075.812500,84171.617188,84171.617188</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>126.539062,625.460938,606.226562,757.101563,894.726562,840.687501,954.734376,1261.749999,361.539062,243.835938,408.039062,161.367188,308.765625,313.250000,290.968750,193.570312,192.726562,207.101562,926.062500,1478.562500,1221.585938,1242.726562,1102.460938,1106.343751</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0.147931,0.727250,0.705145,0.878920,1.037530,0.975346,1.106208,1.456986,0.421817,0.284935,0.476017,0.188747,0.360665,0.365914,0.339859,0.226326,0.225285,0.242124,1.097342,1.763394,1.452151,1.478102,1.309778,1.314391</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0.7742567298217934</v>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>85353.156250,85382.265625,85308.132812,85364.531250,85408.937500,85336.945312,85322.687500,85287.218750,85267.375000,85272.859375,85264.859375,85216.343750,85157.804688,85283.773438,85233.007812,85203.179688,85227.648438,85166.968750,85260.117188,85136.859375,85220.953125,85210.031250,85147.265625,85150.289062</t>
@@ -8338,6 +8394,49 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>85229.210938,85140.296875,85103.109375,85089.312500,85022.687500,84979.375000,84973.320312,84911.109375,84923.335938,84844.226562,84772.593750,84792.640625,84747.984375,84695.671875,84703.093750,84708.093750,84695.625000,84620.875000,84587.250000,84590.140625,84596.171875,84522.031250,84490.781250,84481.414062</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:30</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>24</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>84176.000000,84164.234375,84179.140625,84197.265625,84190.578125,84205.734375,84218.265625,84192.445312,84191.515625,84176.765625,84181.031250,84188.007812,84189.468750,84192.890625,84208.734375,84210.132812,84217.234375,84207.820312,84214.953125,84210.507812,84226.148438,84212.085938,84188.890625,84176.539062</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>84102.890625,84191.820312,84162.265625,84207.195312,84213.710938,84204.492188,84203.789062,84167.429688,84164.601562,84149.859375,84156.835938,84163.312500,84096.554688,84182.687500,84181.781250,84132.296875,84108.789062,84078.187500,84192.242188,84063.171875,84105.750000,84070.593750,84099.203125,84081.742188</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>83667.273438,83560.687500,83491.375000,83462.257812,83378.523438,83324.171875,83284.210938,83194.273438,83111.007812,83023.664062,82977.296875,82974.257812,82937.187500,82895.257812,82862.851562,82808.445312,82783.148438,82743.312500,82611.062500,82565.789062,82581.468750,82567.015625,82525.914062,82464.757812</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>83887.273438,83781.250000,83736.546875,83728.234375,83688.968750,83641.796875,83619.750000,83560.164062,83538.476562,83475.046875,83432.835938,83438.078125,83422.656250,83383.468750,83391.656250,83378.437500,83329.648438,83285.765625,83249.703125,83244.632812,83252.539062,83199.171875,83182.265625,83162.609375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3495,6 +3495,44 @@
       </c>
       <c r="F81" t="n">
         <v>84176.5390625</v>
+      </c>
+      <c r="G81" t="n">
+        <v>82851.703125</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1324.8359375</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1.599044904968572</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1.027650667835813</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:47</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>24</v>
+      </c>
+      <c r="F82" t="n">
+        <v>82747.3203125</v>
       </c>
     </row>
   </sheetData>
@@ -3508,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8424,6 +8462,24 @@
           <t>84176.000000,84164.234375,84179.140625,84197.265625,84190.578125,84205.734375,84218.265625,84192.445312,84191.515625,84176.765625,84181.031250,84188.007812,84189.468750,84192.890625,84208.734375,84210.132812,84217.234375,84207.820312,84214.953125,84210.507812,84226.148438,84212.085938,84188.890625,84176.539062</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>84200.007812,84100.078125,83924.023438,83784.281250,83719.718750,83709.531250,83464.007812,83139.710938,82970.882812,83417.398438,83346.781250,83116.101562,83372.789062,83392.039062,83379.187500,83109.648438,83196.632812,83275.062500,83323.750000,83056.976562,83116.078125,82695.562500,82593.117188,82851.703125</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>24.007812,64.156250,255.117188,412.984375,470.859375,496.203125,754.257812,1052.734374,1220.632812,759.367188,834.250000,1071.906249,816.679688,800.851562,829.546875,1100.484374,1020.601562,932.757812,891.203125,1153.531249,1110.070313,1516.523438,1595.773438,1324.835937</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0.028513,0.076286,0.303986,0.492914,0.562424,0.592768,0.903692,1.266223,1.471158,0.910322,1.000938,1.289649,0.979552,0.960345,0.994909,1.324136,1.226734,1.120093,1.069567,1.388843,1.335566,1.833863,1.932090,1.599045</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>1.027650667835813</v>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>84102.890625,84191.820312,84162.265625,84207.195312,84213.710938,84204.492188,84203.789062,84167.429688,84164.601562,84149.859375,84156.835938,84163.312500,84096.554688,84182.687500,84181.781250,84132.296875,84108.789062,84078.187500,84192.242188,84063.171875,84105.750000,84070.593750,84099.203125,84081.742188</t>
@@ -8437,6 +8493,49 @@
       <c r="M81" t="inlineStr">
         <is>
           <t>83887.273438,83781.250000,83736.546875,83728.234375,83688.968750,83641.796875,83619.750000,83560.164062,83538.476562,83475.046875,83432.835938,83438.078125,83422.656250,83383.468750,83391.656250,83378.437500,83329.648438,83285.765625,83249.703125,83244.632812,83252.539062,83199.171875,83182.265625,83162.609375</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:47</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>24</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>82815.414062,82822.132812,82842.085938,82868.835938,82881.929688,82885.500000,82870.117188,82851.148438,82819.968750,82822.351562,82799.601562,82829.757812,82831.687500,82840.273438,82833.304688,82821.539062,82794.289062,82788.195312,82818.687500,82814.718750,82815.867188,82770.445312,82730.250000,82747.320312</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>82812.679688,82904.312500,82865.460938,82886.750000,82956.507812,82940.484375,82914.929688,82850.898438,82897.914062,82860.492188,82917.312500,82871.726562,82914.687500,82933.875000,82895.179688,82829.132812,82856.148438,82919.812500,82999.265625,82780.710938,82865.929688,82775.078125,82823.562500,82804.390625</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>82484.789062,82419.554688,82326.921875,82315.531250,82249.375000,82185.453125,82147.890625,82098.585938,81971.609375,81914.546875,81854.078125,81883.773438,81848.093750,81801.796875,81797.382812,81698.718750,81669.085938,81606.648438,81512.796875,81508.867188,81451.273438,81376.617188,81347.804688,81303.890625</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>82635.625000,82562.414062,82507.234375,82500.812500,82475.539062,82427.617188,82376.031250,82343.843750,82316.117188,82247.953125,82204.375000,82237.632812,82217.617188,82193.054688,82230.929688,82152.265625,82090.359375,82018.226562,82041.515625,82025.437500,82010.234375,81899.843750,81890.945312,81896.617188</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3533,6 +3533,44 @@
       </c>
       <c r="F82" t="n">
         <v>82747.3203125</v>
+      </c>
+      <c r="G82" t="n">
+        <v>82298.921875</v>
+      </c>
+      <c r="H82" t="n">
+        <v>448.3984375</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.5448412048228912</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.9947783276224145</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:49</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>24</v>
+      </c>
+      <c r="F83" t="n">
+        <v>82214.890625</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +3584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8523,6 +8561,24 @@
           <t>82815.414062,82822.132812,82842.085938,82868.835938,82881.929688,82885.500000,82870.117188,82851.148438,82819.968750,82822.351562,82799.601562,82829.757812,82831.687500,82840.273438,82833.304688,82821.539062,82794.289062,82788.195312,82818.687500,82814.718750,82815.867188,82770.445312,82730.250000,82747.320312</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>82813.601562,82938.671875,82811.968750,83059.867188,82662.000000,82429.117188,82249.437500,82112.101562,82638.890625,80989.343750,80888.109375,80679.742188,81436.046875,81704.578125,81750.789062,81626.039062,81833.296875,81692.789062,81734.703125,81912.062500,82056.156250,82360.210938,82174.703125,82298.921875</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1.812499,116.539063,30.117188,191.031249,219.929688,456.382812,620.679688,739.046876,181.078125,1833.007812,1911.492187,2150.015624,1395.640625,1135.695313,1082.515626,1195.499999,960.992187,1095.406249,1083.984375,902.656250,759.710938,410.234374,555.546875,448.398437</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>0.002189,0.140512,0.036368,0.229992,0.266059,0.553667,0.754631,0.900046,0.219120,2.263270,2.363131,2.664877,1.713787,1.390002,1.324165,1.464606,1.174329,1.340885,1.326223,1.101982,0.925843,0.498098,0.676056,0.544841</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>0.9947783276224145</v>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>82812.679688,82904.312500,82865.460938,82886.750000,82956.507812,82940.484375,82914.929688,82850.898438,82897.914062,82860.492188,82917.312500,82871.726562,82914.687500,82933.875000,82895.179688,82829.132812,82856.148438,82919.812500,82999.265625,82780.710938,82865.929688,82775.078125,82823.562500,82804.390625</t>
@@ -8536,6 +8592,49 @@
       <c r="M82" t="inlineStr">
         <is>
           <t>82635.625000,82562.414062,82507.234375,82500.812500,82475.539062,82427.617188,82376.031250,82343.843750,82316.117188,82247.953125,82204.375000,82237.632812,82217.617188,82193.054688,82230.929688,82152.265625,82090.359375,82018.226562,82041.515625,82025.437500,82010.234375,81899.843750,81890.945312,81896.617188</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:49</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>24</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>82297.976562,82323.679688,82335.492188,82355.156250,82367.820312,82364.257812,82352.984375,82356.851562,82323.523438,82321.195312,82279.382812,82288.500000,82264.515625,82283.429688,82281.523438,82269.515625,82257.695312,82234.046875,82261.492188,82259.539062,82235.234375,82199.671875,82186.343750,82214.890625</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>82293.343750,82343.500000,82370.187500,82343.804688,82394.914062,82403.140625,82428.343750,82360.953125,82374.476562,82379.273438,82328.875000,82332.531250,82366.210938,82389.398438,82372.570312,82352.078125,82320.632812,82387.734375,82415.351562,82286.773438,82335.406250,82276.062500,82297.148438,82326.515625</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>81840.304688,81746.445312,81611.625000,81557.578125,81495.875000,81393.023438,81346.289062,81328.375000,81188.296875,81098.601562,80981.320312,81016.335938,80952.062500,80892.757812,80879.804688,80796.343750,80772.539062,80722.789062,80642.453125,80642.562500,80577.398438,80525.015625,80487.546875,80470.695312</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>82044.015625,81969.929688,81892.000000,81842.265625,81802.093750,81744.328125,81679.625000,81645.679688,81629.085938,81530.164062,81430.609375,81462.929688,81408.195312,81379.601562,81411.156250,81348.734375,81289.070312,81203.921875,81233.242188,81244.445312,81202.718750,81079.664062,81111.960938,81126.515625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3571,6 +3571,44 @@
       </c>
       <c r="F83" t="n">
         <v>82214.890625</v>
+      </c>
+      <c r="G83" t="n">
+        <v>82653.7421875</v>
+      </c>
+      <c r="H83" t="n">
+        <v>438.8515625</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.5309518370075311</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.3927059591640635</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:11</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>24</v>
+      </c>
+      <c r="F84" t="n">
+        <v>82567.5078125</v>
       </c>
     </row>
   </sheetData>
@@ -3584,7 +3622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8622,6 +8660,24 @@
           <t>82297.976562,82323.679688,82335.492188,82355.156250,82367.820312,82364.257812,82352.984375,82356.851562,82323.523438,82321.195312,82279.382812,82288.500000,82264.515625,82283.429688,82281.523438,82269.515625,82257.695312,82234.046875,82261.492188,82259.539062,82235.234375,82199.671875,82186.343750,82214.890625</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>82512.750000,82591.273438,82626.226562,82580.250000,82487.046875,83175.109375,82954.062500,82553.570312,82962.882812,82807.476562,82679.468750,82643.617188,82369.109375,82251.968750,82431.359375,82465.992188,82561.031250,82544.710938,82489.179688,82620.906250,82551.382812,82519.921875,82614.273438,82653.742188</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>214.773438,267.593749,290.734374,225.093750,119.226563,810.851563,601.078125,196.718751,639.359374,486.281251,400.085938,355.117188,104.593750,31.460938,149.835937,196.476562,303.335938,310.664062,227.687499,361.367188,316.148438,320.250000,427.929688,438.851562</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0.260291,0.323998,0.351867,0.272576,0.144540,0.974873,0.724592,0.238292,0.770657,0.587243,0.483900,0.429697,0.126982,0.038249,0.181771,0.238252,0.367408,0.376359,0.276021,0.437380,0.382972,0.388088,0.517985,0.530952</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0.3927059591640635</v>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>82293.343750,82343.500000,82370.187500,82343.804688,82394.914062,82403.140625,82428.343750,82360.953125,82374.476562,82379.273438,82328.875000,82332.531250,82366.210938,82389.398438,82372.570312,82352.078125,82320.632812,82387.734375,82415.351562,82286.773438,82335.406250,82276.062500,82297.148438,82326.515625</t>
@@ -8635,6 +8691,49 @@
       <c r="M83" t="inlineStr">
         <is>
           <t>82044.015625,81969.929688,81892.000000,81842.265625,81802.093750,81744.328125,81679.625000,81645.679688,81629.085938,81530.164062,81430.609375,81462.929688,81408.195312,81379.601562,81411.156250,81348.734375,81289.070312,81203.921875,81233.242188,81244.445312,81202.718750,81079.664062,81111.960938,81126.515625</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:11</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>24</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>82669.007812,82677.054688,82671.476562,82691.898438,82688.703125,82672.265625,82648.343750,82660.703125,82657.437500,82635.882812,82614.476562,82604.632812,82587.242188,82577.304688,82592.632812,82605.304688,82616.914062,82595.593750,82595.492188,82583.695312,82577.109375,82563.531250,82549.429688,82567.507812</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>82671.085938,82645.335938,82671.242188,82711.664062,82696.609375,82655.976562,82619.250000,82617.132812,82580.320312,82673.890625,82594.750000,82573.507812,82618.445312,82574.921875,82578.156250,82606.109375,82633.429688,82563.710938,82583.062500,82562.632812,82569.789062,82545.812500,82504.132812,82527.007812</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>82247.531250,82193.312500,82072.578125,82042.218750,81966.203125,81869.593750,81823.789062,81794.640625,81721.218750,81634.250000,81581.812500,81531.664062,81470.507812,81422.000000,81382.867188,81316.921875,81292.257812,81249.476562,81132.695312,81107.257812,81050.335938,80994.796875,80960.406250,80930.304688</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>82438.085938,82396.625000,82306.593750,82286.031250,82238.914062,82172.070312,82128.070312,82107.328125,82124.132812,82038.234375,81986.648438,81960.656250,81909.679688,81865.257812,81883.882812,81844.492188,81808.968750,81755.085938,81708.695312,81697.289062,81651.351562,81581.968750,81566.539062,81558.000000</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3609,6 +3609,44 @@
       </c>
       <c r="F84" t="n">
         <v>82567.5078125</v>
+      </c>
+      <c r="G84" t="n">
+        <v>82986.7421875</v>
+      </c>
+      <c r="H84" t="n">
+        <v>419.234375</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.5051823507576464</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.314606274482037</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>24</v>
+      </c>
+      <c r="F85" t="n">
+        <v>82960.4140625</v>
       </c>
     </row>
   </sheetData>
@@ -3622,7 +3660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8721,6 +8759,24 @@
           <t>82669.007812,82677.054688,82671.476562,82691.898438,82688.703125,82672.265625,82648.343750,82660.703125,82657.437500,82635.882812,82614.476562,82604.632812,82587.242188,82577.304688,82592.632812,82605.304688,82616.914062,82595.593750,82595.492188,82583.695312,82577.109375,82563.531250,82549.429688,82567.507812</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>82669.312500,82734.570312,82772.273438,82781.929688,82783.242188,82800.687500,82737.210938,82755.210938,82894.882812,82974.351562,82939.679688,83025.859375,82947.429688,83004.609375,82957.257812,82973.140625,83017.328125,82910.640625,82873.320312,82947.851562,83012.000000,82732.093750,82934.367188,82986.742188</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0.304688,57.515624,100.796876,90.031249,94.539062,128.421875,88.867188,94.507812,237.445312,338.468751,325.203126,421.226563,360.187499,427.304687,364.625001,367.835937,400.414063,315.046875,277.828124,364.156251,434.890625,168.562500,384.937499,419.234376</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0.000369,0.069518,0.121776,0.108757,0.114201,0.155098,0.107409,0.114202,0.286441,0.407920,0.392096,0.507344,0.434236,0.514796,0.439534,0.443319,0.482326,0.379984,0.335244,0.439018,0.523889,0.203745,0.464147,0.505182</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0.314606274482037</v>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>82671.085938,82645.335938,82671.242188,82711.664062,82696.609375,82655.976562,82619.250000,82617.132812,82580.320312,82673.890625,82594.750000,82573.507812,82618.445312,82574.921875,82578.156250,82606.109375,82633.429688,82563.710938,82583.062500,82562.632812,82569.789062,82545.812500,82504.132812,82527.007812</t>
@@ -8734,6 +8790,49 @@
       <c r="M84" t="inlineStr">
         <is>
           <t>82438.085938,82396.625000,82306.593750,82286.031250,82238.914062,82172.070312,82128.070312,82107.328125,82124.132812,82038.234375,81986.648438,81960.656250,81909.679688,81865.257812,81883.882812,81844.492188,81808.968750,81755.085938,81708.695312,81697.289062,81651.351562,81581.968750,81566.539062,81558.000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>24</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>82968.562500,82981.703125,82960.273438,82995.085938,82996.281250,82993.937500,82975.523438,82970.023438,82968.664062,82957.132812,82956.335938,82940.093750,82934.867188,82929.664062,82945.523438,82938.867188,82958.335938,82945.609375,82950.703125,82935.382812,82953.656250,82958.984375,82934.054688,82960.414062</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>82977.898438,82974.492188,82968.210938,83053.203125,83049.609375,82977.546875,83007.273438,82948.625000,82949.062500,82993.882812,82989.335938,82946.953125,82993.515625,82982.796875,82930.945312,82967.070312,83008.078125,82955.187500,83003.164062,82985.578125,82968.445312,82974.500000,82928.750000,82946.273438</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>82652.632812,82643.578125,82564.632812,82578.632812,82539.523438,82502.570312,82490.945312,82464.437500,82420.664062,82366.265625,82330.679688,82254.460938,82198.515625,82199.546875,82178.984375,82121.382812,82104.031250,82073.781250,81963.671875,81920.296875,81926.140625,81892.015625,81848.265625,81842.328125</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>82811.304688,82783.578125,82711.382812,82741.640625,82710.562500,82689.851562,82674.015625,82680.164062,82686.960938,82635.289062,82597.984375,82548.335938,82533.882812,82491.320312,82535.671875,82496.226562,82496.054688,82458.867188,82411.781250,82389.132812,82373.742188,82347.507812,82292.687500,82320.304688</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3647,6 +3647,44 @@
       </c>
       <c r="F85" t="n">
         <v>82960.4140625</v>
+      </c>
+      <c r="G85" t="n">
+        <v>83804.3203125</v>
+      </c>
+      <c r="H85" t="n">
+        <v>843.90625</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1.00699611529947</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.5784996801759718</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:31</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>24</v>
+      </c>
+      <c r="F86" t="n">
+        <v>83758.875</v>
       </c>
     </row>
   </sheetData>
@@ -3660,7 +3698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8820,6 +8858,24 @@
           <t>82968.562500,82981.703125,82960.273438,82995.085938,82996.281250,82993.937500,82975.523438,82970.023438,82968.664062,82957.132812,82956.335938,82940.093750,82934.867188,82929.664062,82945.523438,82938.867188,82958.335938,82945.609375,82950.703125,82935.382812,82953.656250,82958.984375,82934.054688,82960.414062</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>83081.968750,82941.070312,82956.570312,82961.117188,82918.031250,83074.468750,83024.281250,82991.750000,83046.820312,83815.710938,83816.367188,83741.523438,83595.187500,83574.953125,83590.132812,83440.562500,83554.132812,83680.593750,83864.273438,83564.968750,83739.687500,83504.710938,84032.812500,83804.320312</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>113.406250,40.632812,3.703126,33.968751,78.250000,80.531250,48.757812,21.726562,78.156251,858.578126,860.031249,801.429688,660.320312,645.289063,644.609374,501.695312,595.796874,734.984375,913.570312,629.585938,786.031250,545.726562,1098.757812,843.906251</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0.136499,0.048990,0.004464,0.040945,0.094370,0.096939,0.058727,0.026179,0.094111,1.024364,1.026090,0.957028,0.789902,0.772108,0.771155,0.601261,0.713067,0.878321,1.089344,0.753409,0.938660,0.653528,1.307534,1.006996</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0.5784996801759718</v>
+      </c>
       <c r="K85" t="inlineStr">
         <is>
           <t>82977.898438,82974.492188,82968.210938,83053.203125,83049.609375,82977.546875,83007.273438,82948.625000,82949.062500,82993.882812,82989.335938,82946.953125,82993.515625,82982.796875,82930.945312,82967.070312,83008.078125,82955.187500,83003.164062,82985.578125,82968.445312,82974.500000,82928.750000,82946.273438</t>
@@ -8833,6 +8889,49 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>82811.304688,82783.578125,82711.382812,82741.640625,82710.562500,82689.851562,82674.015625,82680.164062,82686.960938,82635.289062,82597.984375,82548.335938,82533.882812,82491.320312,82535.671875,82496.226562,82496.054688,82458.867188,82411.781250,82389.132812,82373.742188,82347.507812,82292.687500,82320.304688</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:31</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>24</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>83749.421875,83743.257812,83740.906250,83754.132812,83772.593750,83754.882812,83770.304688,83756.906250,83769.437500,83751.304688,83771.382812,83769.132812,83766.046875,83743.406250,83758.218750,83751.781250,83774.992188,83760.898438,83745.890625,83750.500000,83748.859375,83738.148438,83746.679688,83758.875000</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>83751.382812,83753.484375,83765.437500,83755.804688,83802.976562,83731.890625,83743.273438,83752.000000,83737.664062,83780.789062,83763.625000,83719.390625,83772.500000,83775.609375,83763.046875,83784.578125,83794.250000,83703.851562,83756.117188,83767.218750,83751.882812,83755.554688,83759.851562,83725.921875</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>83429.046875,83343.929688,83272.671875,83253.781250,83211.632812,83143.484375,83127.648438,83106.679688,83054.367188,82996.007812,82978.554688,82946.351562,82870.046875,82834.281250,82778.218750,82720.765625,82716.859375,82671.523438,82532.289062,82490.710938,82481.679688,82455.367188,82419.453125,82395.171875</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>83594.015625,83506.890625,83451.351562,83443.781250,83417.460938,83355.851562,83357.359375,83342.328125,83341.960938,83290.812500,83276.234375,83243.468750,83233.914062,83188.171875,83181.960938,83156.406250,83151.734375,83120.531250,83042.242188,83025.968750,83005.890625,82955.585938,82936.695312,82958.898438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3685,6 +3685,44 @@
       </c>
       <c r="F86" t="n">
         <v>83758.875</v>
+      </c>
+      <c r="G86" t="n">
+        <v>83576.0234375</v>
+      </c>
+      <c r="H86" t="n">
+        <v>182.8515625</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.2187847123843364</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1.166814328690589</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:46</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>24</v>
+      </c>
+      <c r="F87" t="n">
+        <v>83664.625</v>
       </c>
     </row>
   </sheetData>
@@ -3698,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8919,6 +8957,24 @@
           <t>83749.421875,83743.257812,83740.906250,83754.132812,83772.593750,83754.882812,83770.304688,83756.906250,83769.437500,83751.304688,83771.382812,83769.132812,83766.046875,83743.406250,83758.218750,83751.781250,83774.992188,83760.898438,83745.890625,83750.500000,83748.859375,83738.148438,83746.679688,83758.875000</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>84124.992188,83903.687500,83415.007812,83463.343750,83418.718750,83315.773438,82676.906250,82883.203125,82491.460938,82630.210938,82395.578125,82399.000000,82331.710938,82758.078125,82985.476562,82472.617188,82052.421875,81742.500000,81338.523438,82353.500000,82823.671875,83229.757812,83351.476562,83576.023438</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>375.570312,160.429688,325.898438,290.789062,353.875000,439.109374,1093.398438,873.703125,1277.976562,1121.093751,1375.804687,1370.132812,1434.335938,985.328125,772.742188,1279.164062,1722.570313,2018.398438,2407.367188,1397.000000,925.187500,508.390626,395.203126,182.851562</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0.446443,0.191207,0.390695,0.348403,0.424215,0.527042,1.322496,1.054138,1.549223,1.356760,1.669755,1.662803,1.742143,1.190613,0.931178,1.551017,2.099353,2.469215,2.959689,1.696346,1.117057,0.610828,0.474141,0.218785</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>1.166814328690589</v>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>83751.382812,83753.484375,83765.437500,83755.804688,83802.976562,83731.890625,83743.273438,83752.000000,83737.664062,83780.789062,83763.625000,83719.390625,83772.500000,83775.609375,83763.046875,83784.578125,83794.250000,83703.851562,83756.117188,83767.218750,83751.882812,83755.554688,83759.851562,83725.921875</t>
@@ -8932,6 +8988,49 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>83594.015625,83506.890625,83451.351562,83443.781250,83417.460938,83355.851562,83357.359375,83342.328125,83341.960938,83290.812500,83276.234375,83243.468750,83233.914062,83188.171875,83181.960938,83156.406250,83151.734375,83120.531250,83042.242188,83025.968750,83005.890625,82955.585938,82936.695312,82958.898438</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:46</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>24</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>83643.085938,83649.968750,83629.359375,83620.539062,83634.640625,83616.812500,83619.984375,83610.921875,83628.289062,83616.656250,83613.953125,83625.078125,83625.914062,83625.468750,83638.468750,83642.437500,83654.460938,83634.281250,83624.382812,83636.882812,83619.796875,83606.851562,83626.390625,83664.625000</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>83635.304688,83667.132812,83629.304688,83568.453125,83603.367188,83596.359375,83590.382812,83578.109375,83590.757812,83606.109375,83584.835938,83521.328125,83627.382812,83613.140625,83655.929688,83628.500000,83645.023438,83597.109375,83619.601562,83588.765625,83625.132812,83539.070312,83607.898438,83624.726562</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>83127.523438,83003.156250,82855.000000,82796.914062,82721.320312,82645.468750,82584.851562,82489.000000,82454.843750,82384.828125,82340.328125,82309.507812,82255.843750,82216.781250,82180.718750,82124.203125,82119.117188,82072.898438,81947.867188,81932.265625,81940.710938,81899.390625,81881.062500,81888.742188</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>83344.445312,83240.531250,83129.687500,83092.945312,83043.820312,82964.648438,82924.242188,82868.796875,82868.023438,82821.718750,82774.734375,82768.531250,82746.656250,82713.851562,82717.250000,82692.390625,82664.015625,82626.414062,82563.757812,82582.945312,82560.390625,82500.734375,82508.484375,82561.000000</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3723,6 +3723,44 @@
       </c>
       <c r="F87" t="n">
         <v>83664.625</v>
+      </c>
+      <c r="G87" t="n">
+        <v>83770.46875</v>
+      </c>
+      <c r="H87" t="n">
+        <v>105.84375</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.1263497167669842</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.3362016638879464</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:25</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>24</v>
+      </c>
+      <c r="F88" t="n">
+        <v>83815.4296875</v>
       </c>
     </row>
   </sheetData>
@@ -3736,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9018,6 +9056,24 @@
           <t>83643.085938,83649.968750,83629.359375,83620.539062,83634.640625,83616.812500,83619.984375,83610.921875,83628.289062,83616.656250,83613.953125,83625.078125,83625.914062,83625.468750,83638.468750,83642.437500,83654.460938,83634.281250,83624.382812,83636.882812,83619.796875,83606.851562,83626.390625,83664.625000</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>83765.718750,83485.617188,83531.437500,83247.101562,83250.078125,83257.289062,83174.367188,83426.617188,83337.531250,83290.000000,83001.039062,83049.250000,83205.437500,83354.187500,83461.968750,83456.843750,83101.992188,83337.562500,83247.539062,83556.390625,83626.703125,83770.468750,83770.468750,83770.468750</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>122.632812,164.351562,97.921875,373.437499,384.562500,359.523438,445.617188,184.304688,290.757812,326.656250,612.914062,575.828125,420.476562,271.281250,176.500000,185.593750,552.468751,296.718750,376.843749,80.492187,6.906250,163.617188,144.078125,105.843750</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0.146400,0.196862,0.117228,0.448589,0.461937,0.431822,0.535763,0.220918,0.348892,0.392191,0.738441,0.693357,0.505347,0.325456,0.211474,0.222383,0.664808,0.356044,0.452679,0.096333,0.008258,0.195316,0.171992,0.126350</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>0.3362016638879464</v>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>83635.304688,83667.132812,83629.304688,83568.453125,83603.367188,83596.359375,83590.382812,83578.109375,83590.757812,83606.109375,83584.835938,83521.328125,83627.382812,83613.140625,83655.929688,83628.500000,83645.023438,83597.109375,83619.601562,83588.765625,83625.132812,83539.070312,83607.898438,83624.726562</t>
@@ -9031,6 +9087,49 @@
       <c r="M87" t="inlineStr">
         <is>
           <t>83344.445312,83240.531250,83129.687500,83092.945312,83043.820312,82964.648438,82924.242188,82868.796875,82868.023438,82821.718750,82774.734375,82768.531250,82746.656250,82713.851562,82717.250000,82692.390625,82664.015625,82626.414062,82563.757812,82582.945312,82560.390625,82500.734375,82508.484375,82561.000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:25</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>24</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>83722.195312,83726.437500,83714.132812,83726.015625,83726.906250,83721.718750,83710.929688,83703.125000,83693.429688,83678.765625,83663.867188,83680.765625,83677.054688,83681.937500,83712.679688,83737.203125,83754.500000,83760.234375,83766.085938,83771.679688,83792.304688,83775.359375,83776.328125,83815.429688</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>83717.429688,83689.804688,83696.710938,83721.906250,83732.734375,83677.703125,83718.250000,83686.992188,83660.585938,83693.671875,83643.875000,83622.273438,83659.898438,83688.625000,83755.429688,83690.671875,83794.609375,83746.914062,83761.148438,83735.968750,83784.546875,83726.093750,83757.617188,83781.921875</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>83346.789062,83267.296875,83137.500000,83141.539062,83065.226562,83012.929688,82960.812500,82883.101562,82827.554688,82776.609375,82731.937500,82704.320312,82624.898438,82601.484375,82597.039062,82554.375000,82554.632812,82557.492188,82456.101562,82421.187500,82454.554688,82414.554688,82382.664062,82389.226562</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>83507.515625,83439.039062,83354.429688,83338.601562,83303.882812,83252.882812,83229.742188,83185.007812,83159.492188,83110.203125,83072.421875,83068.578125,83031.851562,82998.132812,83025.140625,83030.531250,83005.234375,83008.554688,82976.781250,82971.945312,82980.070312,82937.140625,82925.171875,82959.656250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3761,6 +3761,44 @@
       </c>
       <c r="F88" t="n">
         <v>83815.4296875</v>
+      </c>
+      <c r="G88" t="n">
+        <v>80947.7890625</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2867.640625</v>
+      </c>
+      <c r="I88" t="n">
+        <v>3.542580542608627</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1.944573758970066</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:18:59</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>24</v>
+      </c>
+      <c r="F89" t="n">
+        <v>80722.6015625</v>
       </c>
     </row>
   </sheetData>
@@ -3774,7 +3812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9117,6 +9155,24 @@
           <t>83722.195312,83726.437500,83714.132812,83726.015625,83726.906250,83721.718750,83710.929688,83703.125000,83693.429688,83678.765625,83663.867188,83680.765625,83677.054688,83681.937500,83712.679688,83737.203125,83754.500000,83760.234375,83766.085938,83771.679688,83792.304688,83775.359375,83776.328125,83815.429688</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>83381.156250,83345.492188,83487.023438,83347.679688,83158.328125,83389.601562,83383.671875,82643.960938,82289.007812,81881.406250,81545.281250,81915.867188,81493.523438,81619.132812,81736.367188,81685.687500,81671.289062,81557.046875,81566.281250,81556.296875,81531.742188,81415.750000,80824.382812,80947.789062</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>341.039062,380.945312,227.109374,378.335938,568.578125,332.117188,327.257813,1059.164062,1404.421876,1797.359375,2118.585938,1764.898438,2183.531251,2062.804688,1976.312501,2051.515625,2083.210938,2203.187500,2199.804688,2215.382813,2260.562501,2359.609375,2951.945312,2867.640626</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>0.409012,0.457068,0.272030,0.453925,0.683730,0.398272,0.392472,1.281599,1.706694,2.195076,2.598048,2.154526,2.679392,2.527354,2.417911,2.511475,2.550726,2.701407,2.696954,2.716385,2.772616,2.898222,3.652296,3.542581</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>1.944573758970066</v>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>83717.429688,83689.804688,83696.710938,83721.906250,83732.734375,83677.703125,83718.250000,83686.992188,83660.585938,83693.671875,83643.875000,83622.273438,83659.898438,83688.625000,83755.429688,83690.671875,83794.609375,83746.914062,83761.148438,83735.968750,83784.546875,83726.093750,83757.617188,83781.921875</t>
@@ -9130,6 +9186,49 @@
       <c r="M88" t="inlineStr">
         <is>
           <t>83507.515625,83439.039062,83354.429688,83338.601562,83303.882812,83252.882812,83229.742188,83185.007812,83159.492188,83110.203125,83072.421875,83068.578125,83031.851562,82998.132812,83025.140625,83030.531250,83005.234375,83008.554688,82976.781250,82971.945312,82980.070312,82937.140625,82925.171875,82959.656250</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:18:59</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>24</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>80998.218750,80991.335938,80958.671875,80923.062500,80917.179688,80895.648438,80894.281250,80862.875000,80859.929688,80823.054688,80816.000000,80819.695312,80795.218750,80806.796875,80808.398438,80797.875000,80766.757812,80806.984375,80780.929688,80766.140625,80776.195312,80762.765625,80721.765625,80722.601562</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>80988.703125,81019.398438,80903.984375,80978.820312,80946.429688,80914.210938,80932.992188,80831.078125,80897.062500,80931.445312,80813.140625,80882.734375,80874.585938,80881.203125,80887.625000,80798.093750,80911.453125,80904.945312,80878.898438,80910.921875,80917.867188,80755.062500,80754.125000,80811.515625</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>80601.515625,80502.210938,80379.570312,80324.320312,80227.406250,80156.945312,80148.875000,80059.570312,79993.585938,79920.585938,79884.062500,79880.062500,79800.445312,79784.617188,79733.984375,79654.710938,79623.703125,79595.570312,79470.179688,79405.187500,79405.312500,79364.851562,79345.250000,79267.250000</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>80767.250000,80688.140625,80594.437500,80514.640625,80489.148438,80440.445312,80394.171875,80336.242188,80356.218750,80262.789062,80226.320312,80222.476562,80149.453125,80151.406250,80156.664062,80093.039062,80065.343750,80023.945312,80010.171875,79981.085938,79970.617188,79903.562500,79883.937500,79871.601562</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3799,6 +3799,44 @@
       </c>
       <c r="F89" t="n">
         <v>80722.6015625</v>
+      </c>
+      <c r="G89" t="n">
+        <v>81954.3828125</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1231.78125</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1.503008390433664</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1.183404665131932</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:33</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>24</v>
+      </c>
+      <c r="F90" t="n">
+        <v>81813.4609375</v>
       </c>
     </row>
   </sheetData>
@@ -3812,7 +3850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9216,6 +9254,24 @@
           <t>80998.218750,80991.335938,80958.671875,80923.062500,80917.179688,80895.648438,80894.281250,80862.875000,80859.929688,80823.054688,80816.000000,80819.695312,80795.218750,80806.796875,80808.398438,80797.875000,80766.757812,80806.984375,80780.929688,80766.140625,80776.195312,80762.765625,80721.765625,80722.601562</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>80487.476562,80801.468750,81432.031250,81268.351562,81161.257812,80934.640625,80868.398438,80451.968750,80086.281250,81781.281250,82338.953125,82022.539062,82338.937500,82315.156250,82299.250000,82015.617188,82336.109375,82369.968750,82116.203125,82231.468750,81974.820312,81935.773438,82008.156250,81954.382812</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>510.742188,189.867188,473.359375,345.289062,244.078124,38.992187,25.882812,410.906250,773.648438,958.226562,1522.953125,1202.843751,1543.718750,1508.359375,1490.851562,1217.742188,1569.351563,1562.984375,1335.273437,1465.328125,1198.625001,1173.007812,1286.390625,1231.781251</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>0.634561,0.234980,0.581294,0.424875,0.300732,0.048177,0.032006,0.510747,0.966019,1.171694,1.849614,1.466480,1.874834,1.832420,1.811501,1.484769,1.906031,1.897517,1.626078,1.781955,1.462187,1.431619,1.568613,1.503008</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>1.183404665131932</v>
+      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>80988.703125,81019.398438,80903.984375,80978.820312,80946.429688,80914.210938,80932.992188,80831.078125,80897.062500,80931.445312,80813.140625,80882.734375,80874.585938,80881.203125,80887.625000,80798.093750,80911.453125,80904.945312,80878.898438,80910.921875,80917.867188,80755.062500,80754.125000,80811.515625</t>
@@ -9229,6 +9285,49 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>80767.250000,80688.140625,80594.437500,80514.640625,80489.148438,80440.445312,80394.171875,80336.242188,80356.218750,80262.789062,80226.320312,80222.476562,80149.453125,80151.406250,80156.664062,80093.039062,80065.343750,80023.945312,80010.171875,79981.085938,79970.617188,79903.562500,79883.937500,79871.601562</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:33</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>24</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>81937.554688,81953.781250,81939.320312,81919.773438,81927.203125,81894.296875,81881.781250,81881.046875,81886.179688,81848.593750,81846.500000,81869.382812,81854.203125,81869.976562,81886.335938,81895.914062,81866.140625,81871.492188,81865.648438,81825.164062,81857.351562,81835.820312,81790.765625,81813.460938</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>81933.898438,81968.617188,81889.882812,81964.382812,81935.179688,81877.312500,81863.398438,81856.765625,81926.335938,81917.953125,81836.148438,81875.375000,81843.875000,81882.867188,81933.367188,81898.085938,81948.742188,81919.695312,81901.437500,81848.531250,81891.875000,81860.968750,81787.273438,81822.679688</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>81509.718750,81434.914062,81311.023438,81263.468750,81162.976562,81082.898438,81037.679688,80993.421875,80896.039062,80804.398438,80778.015625,80790.679688,80694.929688,80716.781250,80687.703125,80646.156250,80583.539062,80513.570312,80379.992188,80320.976562,80352.640625,80290.890625,80236.906250,80201.445312</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>81681.710938,81619.851562,81526.484375,81466.648438,81439.851562,81362.062500,81327.953125,81290.750000,81311.734375,81200.718750,81157.664062,81179.671875,81127.062500,81144.554688,81172.671875,81138.968750,81055.437500,80973.679688,80951.359375,80918.828125,80939.101562,80851.273438,80831.062500,80819.257812</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3837,6 +3837,44 @@
       </c>
       <c r="F90" t="n">
         <v>81813.4609375</v>
+      </c>
+      <c r="G90" t="n">
+        <v>81411.8671875</v>
+      </c>
+      <c r="H90" t="n">
+        <v>401.59375</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.4932864997127357</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.4134912400333087</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:41</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>24</v>
+      </c>
+      <c r="F91" t="n">
+        <v>81389.546875</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +3888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9315,6 +9353,24 @@
           <t>81937.554688,81953.781250,81939.320312,81919.773438,81927.203125,81894.296875,81881.781250,81881.046875,81886.179688,81848.593750,81846.500000,81869.382812,81854.203125,81869.976562,81886.335938,81895.914062,81866.140625,81871.492188,81865.648438,81825.164062,81857.351562,81835.820312,81790.765625,81813.460938</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>82052.156250,82079.843750,82186.203125,82139.320312,81913.539062,82116.703125,82528.976562,81942.773438,81919.351562,81865.117188,81240.078125,81334.000000,81088.703125,81018.742188,81467.500000,81611.343750,81561.289062,81666.640625,81500.039062,81443.093750,81413.523438,81352.031250,81450.742188,81411.867188</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>114.601562,126.062500,246.882813,219.546874,13.664062,222.406250,647.195312,61.726562,33.171874,16.523438,606.421875,535.382812,765.500000,851.234374,418.835938,284.570312,304.851562,204.851563,365.609376,382.070312,443.828124,483.789062,340.023438,401.593751</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>0.139669,0.153585,0.300394,0.267286,0.016681,0.270842,0.784204,0.075329,0.040493,0.020184,0.746457,0.658252,0.944028,1.050664,0.514114,0.348690,0.373770,0.250839,0.448600,0.469125,0.545153,0.594686,0.417459,0.493287</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0.4134912400333087</v>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>81933.898438,81968.617188,81889.882812,81964.382812,81935.179688,81877.312500,81863.398438,81856.765625,81926.335938,81917.953125,81836.148438,81875.375000,81843.875000,81882.867188,81933.367188,81898.085938,81948.742188,81919.695312,81901.437500,81848.531250,81891.875000,81860.968750,81787.273438,81822.679688</t>
@@ -9328,6 +9384,49 @@
       <c r="M90" t="inlineStr">
         <is>
           <t>81681.710938,81619.851562,81526.484375,81466.648438,81439.851562,81362.062500,81327.953125,81290.750000,81311.734375,81200.718750,81157.664062,81179.671875,81127.062500,81144.554688,81172.671875,81138.968750,81055.437500,80973.679688,80951.359375,80918.828125,80939.101562,80851.273438,80831.062500,80819.257812</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:41</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>24</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>81388.765625,81401.257812,81427.664062,81416.890625,81420.250000,81412.093750,81391.343750,81378.429688,81379.632812,81356.453125,81350.140625,81356.140625,81345.625000,81358.078125,81362.539062,81367.273438,81370.125000,81393.945312,81395.648438,81376.835938,81397.335938,81375.843750,81351.781250,81389.546875</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>81399.390625,81395.734375,81377.531250,81474.445312,81424.578125,81424.195312,81408.960938,81377.851562,81417.250000,81409.609375,81375.125000,81392.851562,81375.117188,81418.304688,81405.992188,81432.765625,81454.781250,81448.984375,81414.757812,81415.445312,81432.164062,81415.179688,81391.992188,81413.882812</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>81036.328125,80977.250000,80922.265625,80901.015625,80825.921875,80773.421875,80746.484375,80699.867188,80602.476562,80520.625000,80469.851562,80476.351562,80389.171875,80399.960938,80344.343750,80306.000000,80262.250000,80245.078125,80121.015625,80076.570312,80066.218750,80011.773438,79952.773438,79936.500000</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>81187.484375,81139.101562,81090.000000,81060.367188,81026.851562,80992.820312,80960.546875,80921.921875,80929.085938,80842.093750,80785.796875,80780.414062,80741.726562,80739.031250,80742.093750,80729.851562,80691.195312,80654.890625,80634.226562,80608.312500,80597.859375,80515.250000,80488.164062,80497.734375</t>
         </is>
       </c>
     </row>
